--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="专属礼包" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,8 +27,64 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="E3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 自选包
+2 自动开启包</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 可以一键开启
+2 不可以一键</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="350">
   <si>
     <t>_id</t>
   </si>
@@ -41,6 +98,9 @@
     <t>LevelRequired</t>
   </si>
   <si>
+    <t>OpenType</t>
+  </si>
+  <si>
     <t>ItemTypeList</t>
   </si>
   <si>
@@ -65,7 +125,7 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>专属自选1</t>
+    <t>狂斩专属自选</t>
   </si>
   <si>
     <t>12,12,12,12,12,12</t>
@@ -77,54 +137,36 @@
     <t>1,1,1,1,1,1</t>
   </si>
   <si>
-    <t>专属1自选包</t>
-  </si>
-  <si>
-    <t>专属自选2</t>
+    <t>破魂专属自选</t>
   </si>
   <si>
     <t>201,202,203,204,205,206</t>
   </si>
   <si>
-    <t>专属2自选包</t>
-  </si>
-  <si>
-    <t>专属自选3</t>
+    <t>血刃专属自选</t>
   </si>
   <si>
     <t>301,302,303,304,305,306</t>
   </si>
   <si>
-    <t>专属3自选包</t>
-  </si>
-  <si>
-    <t>专属自选4</t>
+    <t>屠龙专属自选</t>
   </si>
   <si>
     <t>401,402,403,404,405,406</t>
   </si>
   <si>
-    <t>专属4自选包</t>
-  </si>
-  <si>
-    <t>专属自选5</t>
+    <t>倚天专属自选</t>
   </si>
   <si>
     <t>501,502,503,504,505,506</t>
   </si>
   <si>
-    <t>专属5自选包</t>
-  </si>
-  <si>
-    <t>专属自选6</t>
+    <t>天命专属自选</t>
   </si>
   <si>
     <t>601,602,603,604,605,606</t>
   </si>
   <si>
-    <t>专属6自选包</t>
-  </si>
-  <si>
     <t>攻略自选包</t>
   </si>
   <si>
@@ -155,7 +197,7 @@
     <t>开天，流星，月灵 三选一</t>
   </si>
   <si>
-    <t>战神时装包</t>
+    <t>斩仙时装包</t>
   </si>
   <si>
     <t>13,13,13,13,13,13,13,13</t>
@@ -167,28 +209,28 @@
     <t>1,1,1,1,1,1,1,1</t>
   </si>
   <si>
-    <t>战神时装一套</t>
-  </si>
-  <si>
-    <t>恶魔时装包</t>
+    <t>斩仙时装一套</t>
+  </si>
+  <si>
+    <t>魔尊时装包</t>
   </si>
   <si>
     <t>3000009,3000010,3000011,3000012,3000013,3000014,3000015,3000016</t>
   </si>
   <si>
-    <t>恶魔时装一套</t>
-  </si>
-  <si>
-    <t>幽灵时装包</t>
+    <t>魔尊时装一套</t>
+  </si>
+  <si>
+    <t>幽冥时装包</t>
   </si>
   <si>
     <t>3000017,3000018,3000019,3000020,3000021,3000022,3000023,3000024</t>
   </si>
   <si>
-    <t>幽灵时装一套</t>
-  </si>
-  <si>
-    <t>专属自选包7</t>
+    <t>幽冥时装一套</t>
+  </si>
+  <si>
+    <t>冰咆哮专属</t>
   </si>
   <si>
     <t>701,702,703,704,705,706</t>
@@ -206,22 +248,892 @@
     <t>2024春节盖楼专属自选包</t>
   </si>
   <si>
-    <t>圣战时装包</t>
+    <t>战魂时装包</t>
   </si>
   <si>
     <t>3000025,3000026,3000027,3000028,3000029,3000030,3000031,3000032</t>
   </si>
   <si>
-    <t>法神时装包</t>
+    <t>战魂时装一套</t>
+  </si>
+  <si>
+    <t>法魂时装包</t>
   </si>
   <si>
     <t>3000033,3000034,3000035,3000036,3000037,3000038,3000039,3000040</t>
   </si>
   <si>
-    <t>天尊时装包</t>
+    <t>法魂时装一套</t>
+  </si>
+  <si>
+    <t>道魂时装包</t>
   </si>
   <si>
     <t>3000041,3000042,3000043,3000044,3000045,3000046,3000047,3000048</t>
+  </si>
+  <si>
+    <t>道魂时装一套</t>
+  </si>
+  <si>
+    <t>法宝自选</t>
+  </si>
+  <si>
+    <t>18,18,18,18,18,18</t>
+  </si>
+  <si>
+    <t>180007,180009,180001,180002,180004,180005</t>
+  </si>
+  <si>
+    <t>特殊法宝自选</t>
+  </si>
+  <si>
+    <t>神技自选1</t>
+  </si>
+  <si>
+    <t>5,5,5,5,5</t>
+  </si>
+  <si>
+    <t>8001,8002,8003,8004,8005</t>
+  </si>
+  <si>
+    <t>神技自选2</t>
+  </si>
+  <si>
+    <t>8006,8007,8008,8009,8010</t>
+  </si>
+  <si>
+    <t>专属自选8</t>
+  </si>
+  <si>
+    <t>12,12,12</t>
+  </si>
+  <si>
+    <t>15,16,17</t>
+  </si>
+  <si>
+    <t>护体，瞬移，隐身专属自选</t>
+  </si>
+  <si>
+    <t>特戒自选</t>
+  </si>
+  <si>
+    <t>19,19,19,19,19,19,19</t>
+  </si>
+  <si>
+    <t>190001,190002,190003,190004,190005,190006</t>
+  </si>
+  <si>
+    <t>升级自选</t>
+  </si>
+  <si>
+    <t>12,12,12,12,12,12,12,12,12,12,12,12</t>
+  </si>
+  <si>
+    <t>807,808,813,816,809,810,814,817,811,812,815,818</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1,1,1,1,1,1</t>
+  </si>
+  <si>
+    <t>初级法宝自选</t>
+  </si>
+  <si>
+    <t>180006,180011,180012,180013,180020,180021</t>
+  </si>
+  <si>
+    <t>18,18,18,18,18,18,18,18,18</t>
+  </si>
+  <si>
+    <t>180001,180002,180004,180005,180007,180008,180009,180018,180019</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1</t>
+  </si>
+  <si>
+    <t>神技自选</t>
+  </si>
+  <si>
+    <t>5,5,5,5,5,5,5,5,5,5</t>
+  </si>
+  <si>
+    <t>8001,8002,8003,8004,8005,8006,8007,8008,8009,8010</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1,1,1</t>
+  </si>
+  <si>
+    <t>10阶技能自选</t>
+  </si>
+  <si>
+    <t>1010,2010,3010</t>
+  </si>
+  <si>
+    <t>地钉，分身，无极 三选一</t>
+  </si>
+  <si>
+    <t>魂骨自选</t>
+  </si>
+  <si>
+    <t>5,5,5,5,5,5,5,5</t>
+  </si>
+  <si>
+    <t>8101,8102,8103,8104,8105,8106,8107,8108</t>
+  </si>
+  <si>
+    <t>11阶技能自选</t>
+  </si>
+  <si>
+    <t>1011,2011,3011</t>
+  </si>
+  <si>
+    <t>战魂，法魂，道魂 三选一</t>
+  </si>
+  <si>
+    <t>极矿工礼包</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>180030</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>极法宝自选</t>
+  </si>
+  <si>
+    <t>180032,180034,180035,180036,180038,180039</t>
+  </si>
+  <si>
+    <t>普通金宠包</t>
+  </si>
+  <si>
+    <t>4,5</t>
+  </si>
+  <si>
+    <t>207,4022</t>
+  </si>
+  <si>
+    <t>2,100000</t>
+  </si>
+  <si>
+    <t>2个40资质金宠+1w口粮</t>
+  </si>
+  <si>
+    <t>满资质金宠包</t>
+  </si>
+  <si>
+    <t>209,4022</t>
+  </si>
+  <si>
+    <t>2,200000</t>
+  </si>
+  <si>
+    <t>2个50资质金宠+5w口粮</t>
+  </si>
+  <si>
+    <t>新手法宝自选</t>
+  </si>
+  <si>
+    <t>180006,180008,180010,180018,180020,180021</t>
+  </si>
+  <si>
+    <t>青龙神器自选</t>
+  </si>
+  <si>
+    <t>61000001,61000002,61000003,61000004,61000005,61000006,61000007,61000008</t>
+  </si>
+  <si>
+    <t>宝石集合包</t>
+  </si>
+  <si>
+    <t>5,5,5,5,5,5,5,5,5,5,5,5</t>
+  </si>
+  <si>
+    <t>60000001,60000002,60000003,60000004,60000005,60000006,60000007,60000008,60000009,60000010</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1,1,1,1,1</t>
+  </si>
+  <si>
+    <t>白虎神器自选</t>
+  </si>
+  <si>
+    <t>61000009,61000010,61000011,61000012,61000013,61000014,61000015,61000016</t>
+  </si>
+  <si>
+    <t>朱雀神器自选</t>
+  </si>
+  <si>
+    <t>61000017,61000018,61000019,61000020,61000021,61000022,61000023,61000024</t>
+  </si>
+  <si>
+    <t>玄武神器自选</t>
+  </si>
+  <si>
+    <t>61000025,61000026,61000027,61000028,61000029,61000030,61000031,61000032</t>
+  </si>
+  <si>
+    <t>麒麟神器自选</t>
+  </si>
+  <si>
+    <t>61000033,61000034,61000035,61000036,61000037,61000038,61000039,61000040</t>
+  </si>
+  <si>
+    <t>全神器自选</t>
+  </si>
+  <si>
+    <t>4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>35,37,38,39,40</t>
+  </si>
+  <si>
+    <t>12阶技能自选</t>
+  </si>
+  <si>
+    <t>1012,2012,3012</t>
+  </si>
+  <si>
+    <t>12技能三选一</t>
+  </si>
+  <si>
+    <t>生肖自选</t>
+  </si>
+  <si>
+    <t>22,22,22,22,22,22,22,22,22,22,22,22</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1</t>
+  </si>
+  <si>
+    <t>极戒自选</t>
+  </si>
+  <si>
+    <t>190007,190008,190009,190010,190011,190012</t>
+  </si>
+  <si>
+    <t>暗金专属自选</t>
+  </si>
+  <si>
+    <t>4,4,4,4,4,4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>1101,1102,1103,1104,1105,1106,1107,1108,1109,1110,1111</t>
+  </si>
+  <si>
+    <t>高级暗金专属</t>
+  </si>
+  <si>
+    <t>1107,1108,1109,1110,1111</t>
+  </si>
+  <si>
+    <t>金色专属自选</t>
+  </si>
+  <si>
+    <t>4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>1001,1002,1003,1010,1011,1012</t>
+  </si>
+  <si>
+    <t>高级金色专属</t>
+  </si>
+  <si>
+    <t>1007,1008,1009,1001,1002,1003,1004,1005,1006,1013,1014</t>
+  </si>
+  <si>
+    <t>驱魔6件套</t>
+  </si>
+  <si>
+    <t>12,12,12,12,12,12,5,5</t>
+  </si>
+  <si>
+    <t>36,37,38,39,40,41,4005,4010</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,300,60</t>
+  </si>
+  <si>
+    <t>盾专属自选套</t>
+  </si>
+  <si>
+    <t>4,4,4,4</t>
+  </si>
+  <si>
+    <t>99,102,104</t>
+  </si>
+  <si>
+    <t>专属自选</t>
+  </si>
+  <si>
+    <t>4,4,4,4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>99,100,101,102,103,104,105,96</t>
+  </si>
+  <si>
+    <t>法力盾4件套</t>
+  </si>
+  <si>
+    <t>12,12,12,12,5,5</t>
+  </si>
+  <si>
+    <t>26,27,28,29,4005,4010</t>
+  </si>
+  <si>
+    <t>1,1,1,1,300,60</t>
+  </si>
+  <si>
+    <t>神雷6件套</t>
+  </si>
+  <si>
+    <t>30,31,32,33,34,35,4005,4010</t>
+  </si>
+  <si>
+    <t>流光6件套</t>
+  </si>
+  <si>
+    <t>5,6,7,8,9,10,4005,4010</t>
+  </si>
+  <si>
+    <t>武神盾4件套</t>
+  </si>
+  <si>
+    <t>11,12,13,14,4005,4010</t>
+  </si>
+  <si>
+    <t>冰咆哮4件套</t>
+  </si>
+  <si>
+    <t>803,804,705,706,4005,4010</t>
+  </si>
+  <si>
+    <t>道力盾4件套</t>
+  </si>
+  <si>
+    <t>18,19,20,21,4005,4010</t>
+  </si>
+  <si>
+    <t>月神4件套</t>
+  </si>
+  <si>
+    <t>22,23,24,25,4005,4010</t>
+  </si>
+  <si>
+    <t>白银礼包</t>
+  </si>
+  <si>
+    <t>15,5,5,5,5,5</t>
+  </si>
+  <si>
+    <t>4014,4012,4001,4011,4102,4010</t>
+  </si>
+  <si>
+    <t>500,2000,10000000,20,200,50</t>
+  </si>
+  <si>
+    <t>经验丹0.5K,传世精华2k,魂环碎片1KW,红装精华3,高级书页200个,专属之心50个</t>
+  </si>
+  <si>
+    <t>黄金礼包</t>
+  </si>
+  <si>
+    <t>180005,180006,180018,180002,180004,180008</t>
+  </si>
+  <si>
+    <t>钻石礼包</t>
+  </si>
+  <si>
+    <t>180007,180009,180001,180002,180004,180019</t>
+  </si>
+  <si>
+    <t>高级法宝自选</t>
+  </si>
+  <si>
+    <t>战士经验红装</t>
+  </si>
+  <si>
+    <t>20,20,20,20,20,20,20,20</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5,6,7,8</t>
+  </si>
+  <si>
+    <t>战士满经验红装自选</t>
+  </si>
+  <si>
+    <t>法师经验红装</t>
+  </si>
+  <si>
+    <t>9,10,11,12,13,14,15,16</t>
+  </si>
+  <si>
+    <t>法师满经验红装自选</t>
+  </si>
+  <si>
+    <t>道士经验红装</t>
+  </si>
+  <si>
+    <t>17,18,19,20,21,22,23,24</t>
+  </si>
+  <si>
+    <t>道士满经验红装自选</t>
+  </si>
+  <si>
+    <t>战士输出红装</t>
+  </si>
+  <si>
+    <t>25,26,27,28,29,30,31,32</t>
+  </si>
+  <si>
+    <t>战士输出红装自选</t>
+  </si>
+  <si>
+    <t>法师输出红装</t>
+  </si>
+  <si>
+    <t>33,34,35,36,37,38,39,40</t>
+  </si>
+  <si>
+    <t>法师输出红装自选</t>
+  </si>
+  <si>
+    <t>道士输出红装</t>
+  </si>
+  <si>
+    <t>20,20,20,20,20,20,20,20,20,20</t>
+  </si>
+  <si>
+    <t>41,42,43,44,45,46,47,48,49,50</t>
+  </si>
+  <si>
+    <t>道士输出红装自选</t>
+  </si>
+  <si>
+    <t>红装自选</t>
+  </si>
+  <si>
+    <t>109,110,111,112,113,114</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>战士暗金</t>
+  </si>
+  <si>
+    <t>151,152,153,154,155,156,157,158</t>
+  </si>
+  <si>
+    <t>法师暗金</t>
+  </si>
+  <si>
+    <t>161,162,163,164,165,166,167,168</t>
+  </si>
+  <si>
+    <t>道士暗金</t>
+  </si>
+  <si>
+    <t>171,172,173,174,175,176,177,178</t>
+  </si>
+  <si>
+    <t>战士平衡金装</t>
+  </si>
+  <si>
+    <t>101,102,103,104,105,106,107,108</t>
+  </si>
+  <si>
+    <t>法师平衡金装</t>
+  </si>
+  <si>
+    <t>109,110,111,112,113,114,115,116</t>
+  </si>
+  <si>
+    <t>道士平衡金装</t>
+  </si>
+  <si>
+    <t>117,118,119,120,121,122,123,124</t>
+  </si>
+  <si>
+    <t>战士防御金装</t>
+  </si>
+  <si>
+    <t>125,126,127,128,129,130,131,132</t>
+  </si>
+  <si>
+    <t>法师输出金装</t>
+  </si>
+  <si>
+    <t>133,134,135,136,137,138,139,140</t>
+  </si>
+  <si>
+    <t>粉色战士</t>
+  </si>
+  <si>
+    <t>181,182,183,184,185,186,187,188</t>
+  </si>
+  <si>
+    <t>粉色法师</t>
+  </si>
+  <si>
+    <t>191,192,193,194,195,196,197,198</t>
+  </si>
+  <si>
+    <t>粉色道士</t>
+  </si>
+  <si>
+    <t>201,202,203,204,205,206,207,208</t>
+  </si>
+  <si>
+    <t>金装自选</t>
+  </si>
+  <si>
+    <t>121,122,123,124,125</t>
+  </si>
+  <si>
+    <t>暗金自选</t>
+  </si>
+  <si>
+    <t>4,4,4</t>
+  </si>
+  <si>
+    <t>118,119,120</t>
+  </si>
+  <si>
+    <t>1,1,1,</t>
+  </si>
+  <si>
+    <t>粉色自选</t>
+  </si>
+  <si>
+    <t>126,127,128</t>
+  </si>
+  <si>
+    <t>40橙宠自选</t>
+  </si>
+  <si>
+    <t>21,21,21</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
+  </si>
+  <si>
+    <t>40资质橙宠自选</t>
+  </si>
+  <si>
+    <t>45橙宠自选</t>
+  </si>
+  <si>
+    <t>4,5,6</t>
+  </si>
+  <si>
+    <t>45资质橙宠自选</t>
+  </si>
+  <si>
+    <t>50橙宠自选</t>
+  </si>
+  <si>
+    <t>7,8,9</t>
+  </si>
+  <si>
+    <t>50资质橙宠自选</t>
+  </si>
+  <si>
+    <t>40红宠自选</t>
+  </si>
+  <si>
+    <t>10,11,12</t>
+  </si>
+  <si>
+    <t>40资质红宠自选</t>
+  </si>
+  <si>
+    <t>45红宠自选</t>
+  </si>
+  <si>
+    <t>13,14,15</t>
+  </si>
+  <si>
+    <t>45资质红宠自选</t>
+  </si>
+  <si>
+    <t>50红宠自选</t>
+  </si>
+  <si>
+    <t>16,17,18</t>
+  </si>
+  <si>
+    <t>50资质红宠自选</t>
+  </si>
+  <si>
+    <t>40金宠自选</t>
+  </si>
+  <si>
+    <t>21,21,21,21,21,21,21,21,21,21,21,21</t>
+  </si>
+  <si>
+    <t>19,20,21,22,23,24,25,26,27,28,29,30</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1,1,1,1</t>
+  </si>
+  <si>
+    <t>40资质金宠自选</t>
+  </si>
+  <si>
+    <t>40金宠自选1</t>
+  </si>
+  <si>
+    <t>21,21,21,21,21,21,21,21,21,21,21,21,21,21,21</t>
+  </si>
+  <si>
+    <t>16,17,18,101,102,103,104,105,106,107,108,109</t>
+  </si>
+  <si>
+    <t>40资质金宠自选1</t>
+  </si>
+  <si>
+    <t>50金宠自选</t>
+  </si>
+  <si>
+    <t>31,32,33,34,35,36,37,38,39,40,41,42</t>
+  </si>
+  <si>
+    <t>50资质金宠自选</t>
+  </si>
+  <si>
+    <t>50金宠自选1</t>
+  </si>
+  <si>
+    <t>21,21,21,21,21,21</t>
+  </si>
+  <si>
+    <t>43,44,45,46,47,48</t>
+  </si>
+  <si>
+    <t>金色刺杀自选</t>
+  </si>
+  <si>
+    <t>1001,1002,1003,1004,1005,1006</t>
+  </si>
+  <si>
+    <t>金色刺杀专属包</t>
+  </si>
+  <si>
+    <t>金色雷电自选</t>
+  </si>
+  <si>
+    <t>1007,1008,1009,1010,1011,1012</t>
+  </si>
+  <si>
+    <t>金色雷电专属包</t>
+  </si>
+  <si>
+    <t>金色火符自选</t>
+  </si>
+  <si>
+    <t>1013,1014,1015,1016,1017,1018</t>
+  </si>
+  <si>
+    <t>金色火符专属包</t>
+  </si>
+  <si>
+    <t>金色战吼自选</t>
+  </si>
+  <si>
+    <t>1019,1020,1021,1022,1023,1024</t>
+  </si>
+  <si>
+    <t>金色战吼专属包</t>
+  </si>
+  <si>
+    <t>金色瞬移自选</t>
+  </si>
+  <si>
+    <t>1025,1026,1027,1028,1029,1030</t>
+  </si>
+  <si>
+    <t>金色瞬移专属包</t>
+  </si>
+  <si>
+    <t>金色隐身自选</t>
+  </si>
+  <si>
+    <t>1031,1032,1033,1034,1035,1036</t>
+  </si>
+  <si>
+    <t>金色隐身专属包</t>
+  </si>
+  <si>
+    <t>金色裂地自选</t>
+  </si>
+  <si>
+    <t>1037,1038,1039,1040,1041,1042</t>
+  </si>
+  <si>
+    <t>金色裂地专属包</t>
+  </si>
+  <si>
+    <t>金色分身自选</t>
+  </si>
+  <si>
+    <t>1043,1044,1045,1046,1047,1048</t>
+  </si>
+  <si>
+    <t>金色分身专属包</t>
+  </si>
+  <si>
+    <t>金色无极自选</t>
+  </si>
+  <si>
+    <t>1049,1050,1051,1052,1053,1054</t>
+  </si>
+  <si>
+    <t>金色无极专属包</t>
+  </si>
+  <si>
+    <t>金色武盾自选</t>
+  </si>
+  <si>
+    <t>1055,1056,1057,1058,1059,1060</t>
+  </si>
+  <si>
+    <t>金色法盾自选</t>
+  </si>
+  <si>
+    <t>1061,1062,1063,1064,1065,1066</t>
+  </si>
+  <si>
+    <t>金色道盾自选</t>
+  </si>
+  <si>
+    <t>1067,1068,1069,1070,1071,1072</t>
+  </si>
+  <si>
+    <t>金色专精自选</t>
+  </si>
+  <si>
+    <t>1073,1074,1075</t>
+  </si>
+  <si>
+    <t>金色盾自选</t>
+  </si>
+  <si>
+    <t>1076,1077,1078</t>
+  </si>
+  <si>
+    <t>暗金1阶自选</t>
+  </si>
+  <si>
+    <t>1101,1102,1103,1104,1105,1106</t>
+  </si>
+  <si>
+    <t>暗金1阶技能专属</t>
+  </si>
+  <si>
+    <t>暗金2阶自选</t>
+  </si>
+  <si>
+    <t>1107,1108,1109,1110,1111,1112</t>
+  </si>
+  <si>
+    <t>暗金2阶技能专属</t>
+  </si>
+  <si>
+    <t>暗金3阶自选</t>
+  </si>
+  <si>
+    <t>1113,1114,1115,1116,1117,1118</t>
+  </si>
+  <si>
+    <t>暗金3阶技能专属</t>
+  </si>
+  <si>
+    <t>暗金4阶自选</t>
+  </si>
+  <si>
+    <t>1119,1120,1121,1122,1123,1124</t>
+  </si>
+  <si>
+    <t>暗金4阶技能专属</t>
+  </si>
+  <si>
+    <t>暗金5阶自选</t>
+  </si>
+  <si>
+    <t>1125,1126,1127,1128,1129,1130</t>
+  </si>
+  <si>
+    <t>暗金5阶技能专属</t>
+  </si>
+  <si>
+    <t>暗金6阶自选</t>
+  </si>
+  <si>
+    <t>1131,1132,1133,1134,1135,1136</t>
+  </si>
+  <si>
+    <t>暗金6阶技能专属</t>
+  </si>
+  <si>
+    <t>暗金7阶自选</t>
+  </si>
+  <si>
+    <t>1137,1138,1139,1140,1141,1142</t>
+  </si>
+  <si>
+    <t>暗金7阶技能专属</t>
+  </si>
+  <si>
+    <t>暗金8阶自选</t>
+  </si>
+  <si>
+    <t>1143,1144,1145,1146,1147,1148</t>
+  </si>
+  <si>
+    <t>暗金8阶技能专属</t>
+  </si>
+  <si>
+    <t>暗金9阶自选</t>
+  </si>
+  <si>
+    <t>1149,1150,1151,1152,1153,1154</t>
+  </si>
+  <si>
+    <t>暗金9阶技能专属</t>
+  </si>
+  <si>
+    <t>暗金10阶自选</t>
+  </si>
+  <si>
+    <t>1155,1156,1157,1158,1159,1160</t>
+  </si>
+  <si>
+    <t>暗金10阶技能专属</t>
+  </si>
+  <si>
+    <t>暗金11阶自选</t>
+  </si>
+  <si>
+    <t>1161,1162,1163,1164,1165,1166</t>
+  </si>
+  <si>
+    <t>暗金11阶技能专属</t>
+  </si>
+  <si>
+    <t>暗金12阶自选</t>
+  </si>
+  <si>
+    <t>1167,1168,1169,1170,1171,1172</t>
+  </si>
+  <si>
+    <t>暗金12阶技能专属</t>
   </si>
 </sst>
 </file>
@@ -234,7 +1146,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,17 +1159,9 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -406,6 +1310,17 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -732,13 +1647,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -747,133 +1665,128 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1193,103 +2106,113 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J22"/>
+  <dimension ref="A3:K111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="5" width="16.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="49.375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="42.25" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="16.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1666666666667" style="1" customWidth="1"/>
+    <col min="6" max="7" width="13.0833333333333" style="3" customWidth="1"/>
+    <col min="8" max="8" width="31.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="72.0166666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="42.25" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" customHeight="1" spans="3:10">
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3" t="s">
+    <row r="3" customHeight="1" spans="3:11">
+      <c r="C3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" customHeight="1" spans="3:10">
-      <c r="C4" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3" t="s">
+    </row>
+    <row r="4" customHeight="1" spans="3:11">
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" customHeight="1" spans="3:10">
-      <c r="C5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="K4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="3:11">
+      <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -1297,20 +2220,23 @@
       <c r="F6" s="1">
         <v>0</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="6" t="s">
+      <c r="G6" s="1">
+        <v>2</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="5" t="s">
         <v>15</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="K6" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1323,51 +2249,57 @@
       <c r="F7" s="1">
         <v>0</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="6" t="s">
+      <c r="G7" s="1">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="J7" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>16</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="J8" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>16</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -1375,25 +2307,28 @@
       <c r="F9" s="1">
         <v>0</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>15</v>
+      <c r="G9" s="1">
+        <v>2</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>16</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -1401,25 +2336,28 @@
       <c r="F10" s="1">
         <v>0</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>15</v>
+      <c r="G10" s="1">
+        <v>2</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>16</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -1427,25 +2365,28 @@
       <c r="F11" s="1">
         <v>0</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>15</v>
+      <c r="G11" s="1">
+        <v>2</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>16</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -1453,155 +2394,173 @@
       <c r="F12" s="1">
         <v>0</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:10">
+      <c r="G12" s="1">
+        <v>2</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:11">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:10">
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:11">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
-      <c r="G14" s="6" t="s">
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>2</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:10">
+      <c r="J14" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:11">
       <c r="C15" s="1">
         <v>10</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="4">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:10">
+      <c r="D15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:11">
       <c r="C16" s="1">
         <v>11</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="4">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0</v>
-      </c>
-      <c r="G16" s="6" t="s">
+      <c r="D16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I16" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H16" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:10">
+      <c r="J16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:11">
       <c r="C17" s="1">
         <v>12</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" s="4">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I17" s="6" t="s">
+      <c r="D17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J17" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C18" s="1">
         <v>13</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -1609,133 +2568,3455 @@
       <c r="F18" s="1">
         <v>0</v>
       </c>
-      <c r="G18" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:10">
+      <c r="G18" s="1">
+        <v>2</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:11">
       <c r="C19" s="1">
         <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
       </c>
-      <c r="F19" s="2">
-        <v>0</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:10">
+      <c r="F19" s="3">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:11">
       <c r="C20" s="1">
         <v>15</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" s="4">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:10">
+      <c r="D20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:11">
       <c r="C21" s="1">
         <v>16</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" s="4">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:10">
+      <c r="D21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:11">
       <c r="C22" s="1">
         <v>17</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:11">
+      <c r="C23" s="1">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E22" s="4">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2">
-        <v>0</v>
-      </c>
-      <c r="G22" s="6" t="s">
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>2</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:11">
+      <c r="C24" s="1">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>2</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:11">
+      <c r="C25" s="1">
+        <v>20</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>2</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C26" s="1">
+        <v>21</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>2</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C27" s="1">
+        <v>22</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:11">
+      <c r="C28" s="1">
+        <v>23</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>2</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:11">
+      <c r="C29" s="1">
+        <v>24</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>2</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:11">
+      <c r="C30" s="1">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1">
+        <v>2</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:11">
+      <c r="C31" s="1">
+        <v>26</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>2</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:11">
+      <c r="C32" s="1">
+        <v>27</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
+        <v>2</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:11">
+      <c r="C33" s="1">
+        <v>28</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
+        <v>2</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:11">
+      <c r="C34" s="1">
+        <v>29</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" s="3">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1">
+        <v>2</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:11">
+      <c r="C35" s="1">
+        <v>30</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1">
+        <v>2</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:11">
+      <c r="C36" s="1">
+        <v>31</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="3">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1">
+        <v>2</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:11">
+      <c r="C37" s="1">
+        <v>32</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E37" s="1">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>2</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:11">
+      <c r="C38" s="1">
+        <v>33</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>2</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1">
+        <v>34</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+      <c r="F39" s="3">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:11">
+      <c r="C40" s="1">
+        <v>35</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="3">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>1</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:11">
+      <c r="C41" s="1">
+        <v>36</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E41" s="1">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="1:11">
+      <c r="C42" s="1">
+        <v>37</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>1</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="1:11">
+      <c r="C43" s="1">
+        <v>38</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E43" s="1">
+        <v>1</v>
+      </c>
+      <c r="F43" s="3">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>1</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="1:11">
+      <c r="C44" s="1">
+        <v>39</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1">
+        <v>1</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="1:11">
+      <c r="C45" s="1">
+        <v>40</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>1</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="1:11">
+      <c r="C46" s="1">
+        <v>41</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E46" s="1">
+        <v>1</v>
+      </c>
+      <c r="F46" s="3">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1">
+        <v>1</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="1:11">
+      <c r="C47" s="1">
+        <v>42</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>2</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1">
         <v>43</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="D48" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+      <c r="F48" s="3">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3">
+        <v>2</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="1:11">
+      <c r="C49" s="1">
+        <v>44</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+      <c r="F49" s="1">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1">
+        <v>2</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+    </row>
+    <row r="51" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1">
+        <v>90</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E51" s="1">
+        <v>1</v>
+      </c>
+      <c r="F51" s="3">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>2</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1">
+        <v>91</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>2</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1">
+        <v>94</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E53" s="1">
+        <v>1</v>
+      </c>
+      <c r="F53" s="3">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>2</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1">
+        <v>95</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E54" s="1">
+        <v>1</v>
+      </c>
+      <c r="F54" s="3">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>2</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="1:11">
+      <c r="C55" s="1">
+        <v>96</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E55" s="1">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1">
+        <v>2</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="1:11">
+      <c r="C56" s="1">
+        <v>97</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E56" s="1">
+        <v>1</v>
+      </c>
+      <c r="F56" s="3">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1">
+        <v>2</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="1:11">
+      <c r="C57" s="1">
+        <v>98</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+      <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>2</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="1:11">
+      <c r="C58" s="1">
+        <v>99</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E58" s="1">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>2</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="1:11">
+      <c r="C59" s="1">
+        <v>100</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E59" s="1">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>2</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="1:11">
+      <c r="C60" s="1">
+        <v>101</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E60" s="1">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>2</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="1:11">
+      <c r="C61" s="1">
+        <v>102</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E61" s="1">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
+        <v>2</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="1:11">
+      <c r="C62" s="1">
+        <v>103</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E62" s="1">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1">
+        <v>2</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="J62" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="1:11">
+      <c r="C63" s="1">
+        <v>104</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E63" s="1">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1">
+        <v>2</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="1:11">
+      <c r="C64" s="1">
+        <v>105</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E64" s="1">
+        <v>0</v>
+      </c>
+      <c r="F64" s="3">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>2</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="1:11">
+      <c r="C66" s="1">
+        <v>106</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E66" s="1">
+        <v>1</v>
+      </c>
+      <c r="F66" s="3">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1">
+        <v>1</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="J66" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="1:11">
+      <c r="C67" s="1">
+        <v>107</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E67" s="1">
+        <v>1</v>
+      </c>
+      <c r="F67" s="3">
+        <v>0</v>
+      </c>
+      <c r="G67" s="1">
+        <v>2</v>
+      </c>
+      <c r="H67" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="I22" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>63</v>
+      <c r="I67" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="J67" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="1:11">
+      <c r="C68" s="1">
+        <v>108</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E68" s="1">
+        <v>1</v>
+      </c>
+      <c r="F68" s="3">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>2</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="J68" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="1:11">
+      <c r="C70" s="1">
+        <v>109</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E70" s="1">
+        <v>1</v>
+      </c>
+      <c r="F70" s="3">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3">
+        <v>2</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="J70" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="1:11">
+      <c r="C71" s="1">
+        <v>110</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E71" s="1">
+        <v>1</v>
+      </c>
+      <c r="F71" s="3">
+        <v>0</v>
+      </c>
+      <c r="G71" s="3">
+        <v>2</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J71" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="1:11">
+      <c r="C72" s="1">
+        <v>111</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E72" s="1">
+        <v>1</v>
+      </c>
+      <c r="F72" s="3">
+        <v>0</v>
+      </c>
+      <c r="G72" s="3">
+        <v>2</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="J72" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="1:11">
+      <c r="C73" s="1">
+        <v>112</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E73" s="1">
+        <v>1</v>
+      </c>
+      <c r="F73" s="3">
+        <v>0</v>
+      </c>
+      <c r="G73" s="3">
+        <v>2</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="J73" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="1:11">
+      <c r="C74" s="1">
+        <v>113</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E74" s="1">
+        <v>1</v>
+      </c>
+      <c r="F74" s="3">
+        <v>0</v>
+      </c>
+      <c r="G74" s="3">
+        <v>2</v>
+      </c>
+      <c r="H74" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="J74" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="1:11">
+      <c r="C75" s="1">
+        <v>114</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E75" s="1">
+        <v>1</v>
+      </c>
+      <c r="F75" s="3">
+        <v>0</v>
+      </c>
+      <c r="G75" s="3">
+        <v>2</v>
+      </c>
+      <c r="H75" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="J75" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="1:11">
+      <c r="C76" s="1">
+        <v>115</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E76" s="1">
+        <v>1</v>
+      </c>
+      <c r="F76" s="3">
+        <v>0</v>
+      </c>
+      <c r="G76" s="3">
+        <v>2</v>
+      </c>
+      <c r="H76" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="J76" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="1:11">
+      <c r="A78" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C78" s="1">
+        <v>118</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E78" s="1">
+        <v>1</v>
+      </c>
+      <c r="F78" s="3">
+        <v>0</v>
+      </c>
+      <c r="G78" s="3">
+        <v>2</v>
+      </c>
+      <c r="H78" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I78" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="J78" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="1:11">
+      <c r="A79" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C79" s="1">
+        <v>119</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E79" s="1">
+        <v>1</v>
+      </c>
+      <c r="F79" s="3">
+        <v>0</v>
+      </c>
+      <c r="G79" s="3">
+        <v>2</v>
+      </c>
+      <c r="H79" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="J79" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="1:11">
+      <c r="A80" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C80" s="1">
+        <v>120</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E80" s="1">
+        <v>1</v>
+      </c>
+      <c r="F80" s="3">
+        <v>0</v>
+      </c>
+      <c r="G80" s="3">
+        <v>2</v>
+      </c>
+      <c r="H80" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="J80" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="1:11">
+      <c r="A81" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C81" s="1">
+        <v>121</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E81" s="1">
+        <v>1</v>
+      </c>
+      <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
+        <v>2</v>
+      </c>
+      <c r="H81" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I81" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="J81" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="1:11">
+      <c r="A82" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C82" s="1">
+        <v>122</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E82" s="1">
+        <v>1</v>
+      </c>
+      <c r="F82" s="3">
+        <v>0</v>
+      </c>
+      <c r="G82" s="3">
+        <v>2</v>
+      </c>
+      <c r="H82" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="J82" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="1:11">
+      <c r="A83" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C83" s="1">
+        <v>123</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E83" s="1">
+        <v>1</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
+        <v>2</v>
+      </c>
+      <c r="H83" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="J83" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="1:11">
+      <c r="A84" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C84" s="1">
+        <v>124</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E84" s="1">
+        <v>1</v>
+      </c>
+      <c r="F84" s="3">
+        <v>0</v>
+      </c>
+      <c r="G84" s="3">
+        <v>2</v>
+      </c>
+      <c r="H84" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="J84" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="1:11">
+      <c r="A85" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C85" s="1">
+        <v>125</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E85" s="1">
+        <v>1</v>
+      </c>
+      <c r="F85" s="3">
+        <v>0</v>
+      </c>
+      <c r="G85" s="3">
+        <v>2</v>
+      </c>
+      <c r="H85" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="J85" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="1:11">
+      <c r="A86" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C86" s="1">
+        <v>126</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E86" s="1">
+        <v>1</v>
+      </c>
+      <c r="F86" s="3">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3">
+        <v>2</v>
+      </c>
+      <c r="H86" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="J86" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="1:11">
+      <c r="A87" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C87" s="1">
+        <v>127</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E87" s="1">
+        <v>1</v>
+      </c>
+      <c r="F87" s="3">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3">
+        <v>2</v>
+      </c>
+      <c r="H87" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="J87" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="1:11">
+      <c r="A88" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C88" s="1">
+        <v>128</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E88" s="1">
+        <v>1</v>
+      </c>
+      <c r="F88" s="3">
+        <v>0</v>
+      </c>
+      <c r="G88" s="3">
+        <v>2</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="J88" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="1:11">
+      <c r="A90" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C90" s="1">
+        <v>137</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E90" s="1">
+        <v>1</v>
+      </c>
+      <c r="F90" s="3">
+        <v>0</v>
+      </c>
+      <c r="G90" s="3">
+        <v>2</v>
+      </c>
+      <c r="H90" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="I90" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="J90" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="1:11">
+      <c r="A91" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C91" s="1">
+        <v>138</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E91" s="1">
+        <v>1</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>2</v>
+      </c>
+      <c r="H91" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="I91" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="J91" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="1:11">
+      <c r="A92" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C92" s="1">
+        <v>139</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E92" s="1">
+        <v>1</v>
+      </c>
+      <c r="F92" s="3">
+        <v>0</v>
+      </c>
+      <c r="G92" s="3">
+        <v>2</v>
+      </c>
+      <c r="H92" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="J92" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="3:11">
+      <c r="C102" s="1">
+        <v>201</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E102" s="1">
+        <v>1</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>2</v>
+      </c>
+      <c r="H102" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I102" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="J102" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="3:11">
+      <c r="C103" s="1">
+        <v>202</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E103" s="1">
+        <v>1</v>
+      </c>
+      <c r="F103" s="3">
+        <v>0</v>
+      </c>
+      <c r="G103" s="3">
+        <v>2</v>
+      </c>
+      <c r="H103" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I103" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="J103" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="3:11">
+      <c r="C104" s="1">
+        <v>203</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E104" s="1">
+        <v>1</v>
+      </c>
+      <c r="F104" s="3">
+        <v>0</v>
+      </c>
+      <c r="G104" s="3">
+        <v>2</v>
+      </c>
+      <c r="H104" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I104" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="J104" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="3:11">
+      <c r="C105" s="1">
+        <v>204</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E105" s="1">
+        <v>1</v>
+      </c>
+      <c r="F105" s="3">
+        <v>0</v>
+      </c>
+      <c r="G105" s="3">
+        <v>2</v>
+      </c>
+      <c r="H105" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I105" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="J105" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="3:11">
+      <c r="C106" s="1">
+        <v>205</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E106" s="1">
+        <v>1</v>
+      </c>
+      <c r="F106" s="3">
+        <v>0</v>
+      </c>
+      <c r="G106" s="3">
+        <v>2</v>
+      </c>
+      <c r="H106" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I106" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="J106" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="3:11">
+      <c r="C107" s="1">
+        <v>206</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E107" s="1">
+        <v>1</v>
+      </c>
+      <c r="F107" s="3">
+        <v>0</v>
+      </c>
+      <c r="G107" s="3">
+        <v>2</v>
+      </c>
+      <c r="H107" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I107" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="J107" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="3:11">
+      <c r="C108" s="1">
+        <v>207</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E108" s="1">
+        <v>1</v>
+      </c>
+      <c r="F108" s="3">
+        <v>0</v>
+      </c>
+      <c r="G108" s="3">
+        <v>2</v>
+      </c>
+      <c r="H108" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="I108" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="J108" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="3:11">
+      <c r="C109" s="1">
+        <v>208</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E109" s="1">
+        <v>1</v>
+      </c>
+      <c r="F109" s="3">
+        <v>0</v>
+      </c>
+      <c r="G109" s="3">
+        <v>2</v>
+      </c>
+      <c r="H109" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="I109" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="J109" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="3:11">
+      <c r="C110" s="1">
+        <v>209</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E110" s="1">
+        <v>1</v>
+      </c>
+      <c r="F110" s="3">
+        <v>0</v>
+      </c>
+      <c r="G110" s="3">
+        <v>2</v>
+      </c>
+      <c r="H110" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="I110" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="J110" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="3:11">
+      <c r="C111" s="1">
+        <v>210</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E111" s="1">
+        <v>1</v>
+      </c>
+      <c r="F111" s="3">
+        <v>0</v>
+      </c>
+      <c r="G111" s="3">
+        <v>2</v>
+      </c>
+      <c r="H111" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="I111" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="J111" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 G3 H3 I3 J3 D4 E4 G4 H4 I4 J4 D5 E5 G5 H5 I5 J5 C3:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5 H3:K5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3 F4:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:G5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,F3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B3:L55"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="3" width="9"/>
+    <col min="4" max="4" width="16.625" customWidth="1"/>
+    <col min="5" max="5" width="12.1666666666667" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="7" width="10.25" customWidth="1"/>
+    <col min="8" max="8" width="30.4166666666667" customWidth="1"/>
+    <col min="9" max="9" width="72.0166666666667" customWidth="1"/>
+    <col min="10" max="10" width="26.875" customWidth="1"/>
+    <col min="11" max="11" width="42.25" customWidth="1"/>
+    <col min="12" max="16384" width="9"/>
+  </cols>
+  <sheetData>
+    <row r="3" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C6" s="1">
+        <v>1001</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>2</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C7" s="1">
+        <v>1002</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C8" s="1">
+        <v>1003</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C9" s="1">
+        <v>1004</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C10" s="1">
+        <v>1005</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C11" s="1">
+        <v>1006</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>2</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C12" s="1">
+        <v>1007</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C13" s="1">
+        <v>1008</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C14" s="1">
+        <v>1009</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>2</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C15" s="1">
+        <v>1010</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C16" s="1">
+        <v>1011</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>2</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C17" s="1">
+        <v>1012</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C18" s="1">
+        <v>1013</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>2</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C19" s="1">
+        <v>1014</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="18" customHeight="1"/>
+    <row r="21" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C21" s="1">
+        <v>1101</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>2</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C22" s="1">
+        <v>1102</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>2</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C23" s="1">
+        <v>1103</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>2</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C24" s="1">
+        <v>1104</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>2</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C25" s="1">
+        <v>1105</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>2</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C26" s="1">
+        <v>1106</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>2</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C27" s="1">
+        <v>1107</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C28" s="1">
+        <v>1108</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>2</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C29" s="1">
+        <v>1109</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>2</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C30" s="1">
+        <v>1110</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1">
+        <v>2</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C31" s="1">
+        <v>1111</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>2</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
+      <c r="C32" s="1">
+        <v>1112</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
+        <v>2</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B33"/>
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
+      <c r="H33"/>
+      <c r="I33"/>
+      <c r="J33"/>
+      <c r="K33"/>
+      <c r="L33"/>
+    </row>
+    <row r="35" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B35"/>
+      <c r="C35"/>
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35"/>
+      <c r="H35"/>
+      <c r="I35"/>
+      <c r="J35"/>
+      <c r="K35"/>
+      <c r="L35"/>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B36"/>
+      <c r="C36"/>
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="F36"/>
+      <c r="G36"/>
+      <c r="H36"/>
+      <c r="I36"/>
+      <c r="J36"/>
+      <c r="K36"/>
+      <c r="L36"/>
+    </row>
+    <row r="47" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B47"/>
+      <c r="C47"/>
+      <c r="D47"/>
+      <c r="E47"/>
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="H47"/>
+      <c r="I47"/>
+      <c r="J47"/>
+      <c r="K47"/>
+      <c r="L47"/>
+    </row>
+    <row r="48" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B48"/>
+      <c r="C48"/>
+      <c r="D48"/>
+      <c r="E48"/>
+      <c r="F48"/>
+      <c r="G48"/>
+      <c r="H48"/>
+      <c r="I48"/>
+      <c r="J48"/>
+      <c r="K48"/>
+      <c r="L48"/>
+    </row>
+    <row r="49" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B49"/>
+      <c r="C49"/>
+      <c r="D49"/>
+      <c r="E49"/>
+      <c r="F49"/>
+      <c r="G49"/>
+      <c r="H49"/>
+      <c r="I49"/>
+      <c r="J49"/>
+      <c r="K49"/>
+      <c r="L49"/>
+    </row>
+    <row r="50" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B50"/>
+      <c r="C50"/>
+      <c r="D50"/>
+      <c r="E50"/>
+      <c r="F50"/>
+      <c r="G50"/>
+      <c r="H50"/>
+      <c r="I50"/>
+      <c r="J50"/>
+      <c r="K50"/>
+      <c r="L50"/>
+    </row>
+    <row r="51" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B51"/>
+      <c r="C51"/>
+      <c r="D51"/>
+      <c r="E51"/>
+      <c r="F51"/>
+      <c r="G51"/>
+      <c r="H51"/>
+      <c r="I51"/>
+      <c r="J51"/>
+      <c r="K51"/>
+      <c r="L51"/>
+    </row>
+    <row r="52" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B52"/>
+      <c r="C52"/>
+      <c r="D52"/>
+      <c r="E52"/>
+      <c r="F52"/>
+      <c r="G52"/>
+      <c r="H52"/>
+      <c r="I52"/>
+      <c r="J52"/>
+      <c r="K52"/>
+      <c r="L52"/>
+    </row>
+    <row r="53" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B53"/>
+      <c r="C53"/>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53"/>
+      <c r="G53"/>
+      <c r="H53"/>
+      <c r="I53"/>
+      <c r="J53"/>
+      <c r="K53"/>
+      <c r="L53"/>
+    </row>
+    <row r="54" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B54"/>
+      <c r="C54"/>
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="F54"/>
+      <c r="G54"/>
+      <c r="H54"/>
+      <c r="I54"/>
+      <c r="J54"/>
+      <c r="K54"/>
+      <c r="L54"/>
+    </row>
+    <row r="55" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">
+      <c r="B55"/>
+      <c r="C55"/>
+      <c r="D55"/>
+      <c r="E55"/>
+      <c r="F55"/>
+      <c r="G55"/>
+      <c r="H55"/>
+      <c r="I55"/>
+      <c r="J55"/>
+      <c r="K55"/>
+      <c r="L55"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="346">
   <si>
     <t>_id</t>
   </si>
@@ -125,117 +125,111 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>狂斩专属自选</t>
+    <t>1阶技能自选</t>
+  </si>
+  <si>
+    <t>3,3,3</t>
+  </si>
+  <si>
+    <t>1001,2001,3001</t>
+  </si>
+  <si>
+    <t>1,1,1</t>
+  </si>
+  <si>
+    <t>2阶技能自选</t>
+  </si>
+  <si>
+    <t>1002,2002,3002</t>
+  </si>
+  <si>
+    <t>3阶技能自选</t>
+  </si>
+  <si>
+    <t>1003,2003,3003</t>
+  </si>
+  <si>
+    <t>4阶技能自选</t>
+  </si>
+  <si>
+    <t>1004,2004,3004</t>
+  </si>
+  <si>
+    <t>5阶技能自选</t>
+  </si>
+  <si>
+    <t>1005,2005,3005</t>
+  </si>
+  <si>
+    <t>6阶技能自选</t>
+  </si>
+  <si>
+    <t>1006,2006,3006</t>
+  </si>
+  <si>
+    <t>7阶技能自选</t>
+  </si>
+  <si>
+    <t>1007,2007,3007</t>
+  </si>
+  <si>
+    <t>8介技能自选</t>
+  </si>
+  <si>
+    <t>1008,2008,3008</t>
+  </si>
+  <si>
+    <t>9介技能自选</t>
+  </si>
+  <si>
+    <t>1009,2009,3009</t>
+  </si>
+  <si>
+    <t>新手宠物礼包</t>
+  </si>
+  <si>
+    <t>21,21,21</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
+  </si>
+  <si>
+    <t>魔尊时装包</t>
+  </si>
+  <si>
+    <t>13,13,13,13,13,13,13,13</t>
+  </si>
+  <si>
+    <t>3000009,3000010,3000011,3000012,3000013,3000014,3000015,3000016</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1</t>
+  </si>
+  <si>
+    <t>魔尊时装一套</t>
+  </si>
+  <si>
+    <t>幽冥时装包</t>
+  </si>
+  <si>
+    <t>3000017,3000018,3000019,3000020,3000021,3000022,3000023,3000024</t>
+  </si>
+  <si>
+    <t>幽冥时装一套</t>
+  </si>
+  <si>
+    <t>冰咆哮专属</t>
   </si>
   <si>
     <t>12,12,12,12,12,12</t>
   </si>
   <si>
-    <t>101,102,103,104,105,106</t>
+    <t>701,702,703,704,705,706</t>
   </si>
   <si>
     <t>1,1,1,1,1,1</t>
   </si>
   <si>
-    <t>破魂专属自选</t>
-  </si>
-  <si>
-    <t>201,202,203,204,205,206</t>
-  </si>
-  <si>
-    <t>血刃专属自选</t>
-  </si>
-  <si>
-    <t>301,302,303,304,305,306</t>
-  </si>
-  <si>
-    <t>屠龙专属自选</t>
-  </si>
-  <si>
-    <t>401,402,403,404,405,406</t>
-  </si>
-  <si>
-    <t>倚天专属自选</t>
-  </si>
-  <si>
-    <t>501,502,503,504,505,506</t>
-  </si>
-  <si>
-    <t>天命专属自选</t>
-  </si>
-  <si>
-    <t>601,602,603,604,605,606</t>
-  </si>
-  <si>
-    <t>攻略自选包</t>
-  </si>
-  <si>
-    <t>1,2,3,4,5,6</t>
-  </si>
-  <si>
-    <t>8介技能自选</t>
-  </si>
-  <si>
-    <t>3,3,3</t>
-  </si>
-  <si>
-    <t>1008,2008,3008</t>
-  </si>
-  <si>
-    <t>1,1,1</t>
-  </si>
-  <si>
-    <t>护体，瞬移，隐身 三选一</t>
-  </si>
-  <si>
-    <t>9介技能自选</t>
-  </si>
-  <si>
-    <t>1009,2009,3009</t>
-  </si>
-  <si>
-    <t>开天，流星，月灵 三选一</t>
-  </si>
-  <si>
-    <t>斩仙时装包</t>
-  </si>
-  <si>
-    <t>13,13,13,13,13,13,13,13</t>
-  </si>
-  <si>
-    <t>3000001,3000002,3000003,3000004,3000005,3000006,3000007,3000008</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,1,1</t>
-  </si>
-  <si>
-    <t>斩仙时装一套</t>
-  </si>
-  <si>
-    <t>魔尊时装包</t>
-  </si>
-  <si>
-    <t>3000009,3000010,3000011,3000012,3000013,3000014,3000015,3000016</t>
-  </si>
-  <si>
-    <t>魔尊时装一套</t>
-  </si>
-  <si>
-    <t>幽冥时装包</t>
-  </si>
-  <si>
-    <t>3000017,3000018,3000019,3000020,3000021,3000022,3000023,3000024</t>
-  </si>
-  <si>
-    <t>幽冥时装一套</t>
-  </si>
-  <si>
-    <t>冰咆哮专属</t>
-  </si>
-  <si>
-    <t>701,702,703,704,705,706</t>
-  </si>
-  <si>
     <t>节日冰咆哮专属自选包</t>
   </si>
   <si>
@@ -816,12 +810,6 @@
   </si>
   <si>
     <t>40橙宠自选</t>
-  </si>
-  <si>
-    <t>21,21,21</t>
-  </si>
-  <si>
-    <t>1,2,3</t>
   </si>
   <si>
     <t>40资质橙宠自选</t>
@@ -2106,7 +2094,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:K111"/>
+  <dimension ref="A3:K112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2420,23 +2408,23 @@
       <c r="E13" s="1">
         <v>1</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1">
         <v>2</v>
       </c>
       <c r="H13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="I13" s="5" t="s">
-        <v>31</v>
-      </c>
       <c r="J13" s="5" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:11">
@@ -2444,28 +2432,28 @@
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="1">
         <v>0</v>
       </c>
       <c r="G14" s="1">
         <v>2</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:11">
@@ -2473,181 +2461,152 @@
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
       </c>
-      <c r="G15" s="1">
-        <v>1</v>
+      <c r="G15" s="3">
+        <v>2</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:11">
-      <c r="C16" s="1">
-        <v>11</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="1">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3">
-        <v>0</v>
-      </c>
-      <c r="G16" s="1">
-        <v>1</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:11">
       <c r="C17" s="1">
+        <v>11</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:11">
+      <c r="C18" s="1">
         <v>12</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C19" s="1">
+        <v>13</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2</v>
+      </c>
+      <c r="H19" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="1">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="1">
-        <v>1</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I17" s="5" t="s">
+      <c r="I19" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="J17" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K17" s="1" t="s">
+      <c r="J19" s="5" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C18" s="1">
-        <v>13</v>
-      </c>
-      <c r="D18" s="1" t="s">
+      <c r="K19" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="E18" s="1">
-        <v>1</v>
-      </c>
-      <c r="F18" s="1">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1">
-        <v>2</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:11">
-      <c r="C19" s="1">
-        <v>14</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="3">
-        <v>0</v>
-      </c>
-      <c r="G19" s="1">
-        <v>2</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:11">
       <c r="C20" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:11">
       <c r="C21" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E21" s="1">
         <v>0</v>
@@ -2659,24 +2618,24 @@
         <v>1</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:11">
       <c r="C22" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E22" s="1">
         <v>0</v>
@@ -2688,53 +2647,53 @@
         <v>1</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:11">
       <c r="C23" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="3">
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:11">
       <c r="C24" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -2746,169 +2705,169 @@
         <v>2</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:11">
       <c r="C25" s="1">
+        <v>19</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>2</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:11">
+      <c r="C26" s="1">
         <v>20</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E25" s="1">
-        <v>1</v>
-      </c>
-      <c r="F25" s="3">
-        <v>0</v>
-      </c>
-      <c r="G25" s="1">
-        <v>2</v>
-      </c>
-      <c r="H25" s="5" t="s">
+      <c r="D26" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I25" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C26" s="1">
-        <v>21</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="E26" s="1">
         <v>1</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="3">
         <v>0</v>
       </c>
       <c r="G26" s="1">
         <v>2</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C27" s="1">
+        <v>21</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C28" s="1">
         <v>22</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D28" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>2</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I28" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E27" s="1">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1">
-        <v>0</v>
-      </c>
-      <c r="G27" s="1">
-        <v>2</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:11">
-      <c r="C28" s="1">
-        <v>23</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E28" s="1">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1">
-        <v>0</v>
-      </c>
-      <c r="G28" s="1">
-        <v>2</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>81</v>
-      </c>
       <c r="J28" s="5" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:11">
       <c r="C29" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="1">
         <v>0</v>
       </c>
       <c r="G29" s="1">
         <v>2</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:11">
       <c r="C30" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -2920,24 +2879,24 @@
         <v>2</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:11">
       <c r="C31" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -2949,24 +2908,24 @@
         <v>2</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:11">
       <c r="C32" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -2978,24 +2937,24 @@
         <v>2</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:11">
       <c r="C33" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -3007,24 +2966,24 @@
         <v>2</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>97</v>
+        <v>14</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:11">
       <c r="C34" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -3036,24 +2995,24 @@
         <v>2</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>99</v>
+        <v>94</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:11">
       <c r="C35" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -3065,24 +3024,24 @@
         <v>2</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>104</v>
+        <v>16</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:11">
       <c r="C36" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
@@ -3094,27 +3053,27 @@
         <v>2</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>40</v>
+        <v>102</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:11">
       <c r="C37" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="3">
         <v>0</v>
@@ -3123,171 +3082,171 @@
         <v>2</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>108</v>
+        <v>62</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>110</v>
+        <v>39</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:11">
       <c r="C38" s="1">
+        <v>32</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>2</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:11">
+      <c r="C39" s="1">
         <v>33</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D39" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E39" s="1">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>2</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="J39" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E38" s="1">
-        <v>0</v>
-      </c>
-      <c r="F38" s="3">
-        <v>0</v>
-      </c>
-      <c r="G38" s="1">
-        <v>2</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="I38" s="5" t="s">
+      <c r="K39" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="J38" s="5" t="s">
+    </row>
+    <row r="40" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1">
+        <v>34</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="3">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>2</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I40" s="5" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="39" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1">
-        <v>34</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E39" s="1">
-        <v>1</v>
-      </c>
-      <c r="F39" s="3">
-        <v>0</v>
-      </c>
-      <c r="G39">
-        <v>2</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="J39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="1:11">
-      <c r="C40" s="1">
-        <v>35</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E40" s="1">
-        <v>1</v>
-      </c>
-      <c r="F40" s="3">
-        <v>0</v>
-      </c>
-      <c r="G40" s="1">
-        <v>1</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>119</v>
-      </c>
       <c r="J40" s="5" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:11">
       <c r="C41" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="3">
         <v>0</v>
       </c>
-      <c r="G41" s="3">
+      <c r="G41" s="1">
         <v>1</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:11">
       <c r="C42" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
-      <c r="G42" s="1">
+      <c r="G42" s="3">
         <v>1</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:11">
       <c r="C43" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E43" s="1">
         <v>1</v>
@@ -3299,24 +3258,24 @@
         <v>1</v>
       </c>
       <c r="H43" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="J43" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="I43" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="J43" s="5" t="s">
-        <v>91</v>
-      </c>
       <c r="K43" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:11">
       <c r="C44" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -3328,24 +3287,24 @@
         <v>1</v>
       </c>
       <c r="H44" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="J44" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="I44" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="J44" s="5" t="s">
-        <v>91</v>
-      </c>
       <c r="K44" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:11">
       <c r="C45" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -3357,24 +3316,24 @@
         <v>1</v>
       </c>
       <c r="H45" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="J45" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="I45" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="J45" s="5" t="s">
-        <v>91</v>
-      </c>
       <c r="K45" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:11">
       <c r="C46" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
@@ -3386,159 +3345,157 @@
         <v>1</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:11">
       <c r="C47" s="1">
+        <v>41</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>1</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="1:11">
+      <c r="C48" s="1">
         <v>42</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D48" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+      <c r="F48" s="3">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1">
+        <v>2</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K48" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E47" s="1">
-        <v>1</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="1">
-        <v>2</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I47" s="5" t="s">
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1">
+        <v>43</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="J47" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K47" s="1" t="s">
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
+        <v>2</v>
+      </c>
+      <c r="H49" s="5" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="48" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1">
-        <v>43</v>
-      </c>
-      <c r="D48" s="1" t="s">
+      <c r="I49" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="E48" s="1">
-        <v>1</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>2</v>
-      </c>
-      <c r="H48" s="5" t="s">
+      <c r="J49" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="I48" s="5" t="s">
+      <c r="K49" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="1:11">
+      <c r="C50" s="1">
+        <v>44</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="J48" s="5" t="s">
+      <c r="E50" s="1">
+        <v>1</v>
+      </c>
+      <c r="F50" s="1">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1">
+        <v>2</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I50" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="K48" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C49" s="1">
-        <v>44</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E49" s="1">
-        <v>1</v>
-      </c>
-      <c r="F49" s="1">
-        <v>0</v>
-      </c>
-      <c r="G49" s="1">
-        <v>2</v>
-      </c>
-      <c r="H49" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I49" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="J49" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="50" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
+      <c r="J50" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="1:11">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
-      <c r="C51" s="1">
-        <v>90</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E51" s="1">
-        <v>1</v>
-      </c>
-      <c r="F51" s="3">
-        <v>0</v>
-      </c>
-      <c r="G51" s="1">
-        <v>2</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="I51" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J51" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>144</v>
-      </c>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="1:11">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -3550,26 +3507,26 @@
         <v>2</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="1:11">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E53" s="1">
         <v>1</v>
@@ -3581,58 +3538,60 @@
         <v>2</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="1:11">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1">
+        <v>94</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E54" s="1">
+        <v>1</v>
+      </c>
+      <c r="F54" s="3">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>2</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1">
         <v>95</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E54" s="1">
-        <v>1</v>
-      </c>
-      <c r="F54" s="3">
-        <v>0</v>
-      </c>
-      <c r="G54" s="1">
-        <v>2</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="I54" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="J54" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="1:11">
-      <c r="C55" s="1">
-        <v>96</v>
-      </c>
       <c r="D55" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="3">
         <v>0</v>
@@ -3641,27 +3600,27 @@
         <v>2</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>157</v>
+        <v>89</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="1:11">
       <c r="C56" s="1">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E56" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" s="3">
         <v>0</v>
@@ -3670,24 +3629,24 @@
         <v>2</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>32</v>
+        <v>155</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:11">
       <c r="C57" s="1">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -3699,27 +3658,27 @@
         <v>2</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="1:11">
       <c r="C58" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -3728,24 +3687,24 @@
         <v>2</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>167</v>
+        <v>89</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="1:11">
       <c r="C59" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
@@ -3757,24 +3716,24 @@
         <v>2</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="1:11">
       <c r="C60" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
@@ -3786,24 +3745,24 @@
         <v>2</v>
       </c>
       <c r="H60" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="J60" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="I60" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="J60" s="5" t="s">
-        <v>157</v>
-      </c>
       <c r="K60" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="1:11">
       <c r="C61" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
@@ -3815,24 +3774,24 @@
         <v>2</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="1:11">
       <c r="C62" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E62" s="1">
         <v>0</v>
@@ -3844,24 +3803,24 @@
         <v>2</v>
       </c>
       <c r="H62" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="J62" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="I62" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="J62" s="5" t="s">
-        <v>167</v>
-      </c>
       <c r="K62" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="1:11">
       <c r="C63" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
@@ -3873,82 +3832,82 @@
         <v>2</v>
       </c>
       <c r="H63" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="J63" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="I63" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="J63" s="5" t="s">
-        <v>167</v>
-      </c>
       <c r="K63" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="1:11">
       <c r="C64" s="1">
+        <v>104</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E64" s="1">
+        <v>0</v>
+      </c>
+      <c r="F64" s="3">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>2</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="1:11">
+      <c r="C65" s="1">
         <v>105</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E64" s="1">
-        <v>0</v>
-      </c>
-      <c r="F64" s="3">
-        <v>0</v>
-      </c>
-      <c r="G64" s="1">
-        <v>2</v>
-      </c>
-      <c r="H64" s="5" t="s">
+      <c r="D65" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E65" s="1">
+        <v>0</v>
+      </c>
+      <c r="F65" s="3">
+        <v>0</v>
+      </c>
+      <c r="G65" s="1">
+        <v>2</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="J65" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="I64" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="J64" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" spans="1:11">
-      <c r="C66" s="1">
-        <v>106</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E66" s="1">
-        <v>1</v>
-      </c>
-      <c r="F66" s="3">
-        <v>0</v>
-      </c>
-      <c r="G66" s="1">
-        <v>1</v>
-      </c>
-      <c r="H66" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="I66" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="J66" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>184</v>
+      <c r="K65" s="1" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="1:11">
       <c r="C67" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E67" s="1">
         <v>1</v>
@@ -3957,85 +3916,85 @@
         <v>0</v>
       </c>
       <c r="G67" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>64</v>
+        <v>179</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>40</v>
+        <v>181</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>83</v>
+        <v>182</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="1:11">
       <c r="C68" s="1">
+        <v>107</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E68" s="1">
+        <v>1</v>
+      </c>
+      <c r="F68" s="3">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>2</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="J68" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="1:11">
+      <c r="C69" s="1">
         <v>108</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D69" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1</v>
+      </c>
+      <c r="F69" s="3">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1">
+        <v>2</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="J69" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K69" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="E68" s="1">
-        <v>1</v>
-      </c>
-      <c r="F68" s="3">
-        <v>0</v>
-      </c>
-      <c r="G68" s="1">
-        <v>2</v>
-      </c>
-      <c r="H68" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I68" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="J68" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="70" customHeight="1" spans="1:11">
-      <c r="C70" s="1">
-        <v>109</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E70" s="1">
-        <v>1</v>
-      </c>
-      <c r="F70" s="3">
-        <v>0</v>
-      </c>
-      <c r="G70" s="3">
-        <v>2</v>
-      </c>
-      <c r="H70" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="I70" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="J70" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="1:11">
       <c r="C71" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -4047,24 +4006,24 @@
         <v>2</v>
       </c>
       <c r="H71" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J71" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="K71" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="I71" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="J71" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="1:11">
       <c r="C72" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -4076,24 +4035,24 @@
         <v>2</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="1:11">
       <c r="C73" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -4105,24 +4064,24 @@
         <v>2</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="1:11">
       <c r="C74" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -4134,24 +4093,24 @@
         <v>2</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="1:11">
       <c r="C75" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -4163,129 +4122,123 @@
         <v>2</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I75" s="5" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="1:11">
       <c r="C76" s="1">
+        <v>114</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E76" s="1">
+        <v>1</v>
+      </c>
+      <c r="F76" s="3">
+        <v>0</v>
+      </c>
+      <c r="G76" s="3">
+        <v>2</v>
+      </c>
+      <c r="H76" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="J76" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="1:11">
+      <c r="C77" s="1">
         <v>115</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="E76" s="1">
-        <v>1</v>
-      </c>
-      <c r="F76" s="3">
-        <v>0</v>
-      </c>
-      <c r="G76" s="3">
-        <v>2</v>
-      </c>
-      <c r="H76" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="I76" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="J76" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="78" customHeight="1" spans="1:11">
-      <c r="A78" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C78" s="1">
-        <v>118</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E78" s="1">
-        <v>1</v>
-      </c>
-      <c r="F78" s="3">
-        <v>0</v>
-      </c>
-      <c r="G78" s="3">
-        <v>2</v>
-      </c>
-      <c r="H78" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="I78" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="J78" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K78" s="3" t="s">
-        <v>213</v>
+      <c r="D77" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E77" s="1">
+        <v>1</v>
+      </c>
+      <c r="F77" s="3">
+        <v>0</v>
+      </c>
+      <c r="G77" s="3">
+        <v>2</v>
+      </c>
+      <c r="H77" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="J77" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="1:11">
       <c r="A79" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C79" s="1">
+        <v>118</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E79" s="1">
+        <v>1</v>
+      </c>
+      <c r="F79" s="3">
+        <v>0</v>
+      </c>
+      <c r="G79" s="3">
+        <v>2</v>
+      </c>
+      <c r="H79" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="I79" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C79" s="1">
-        <v>119</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E79" s="1">
-        <v>1</v>
-      </c>
-      <c r="F79" s="3">
-        <v>0</v>
-      </c>
-      <c r="G79" s="3">
-        <v>2</v>
-      </c>
-      <c r="H79" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="I79" s="5" t="s">
-        <v>216</v>
-      </c>
       <c r="J79" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="1:11">
       <c r="A80" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C80" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
@@ -4297,30 +4250,30 @@
         <v>2</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="1:11">
       <c r="A81" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C81" s="1">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E81" s="1">
         <v>1</v>
@@ -4332,30 +4285,30 @@
         <v>2</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="1:11">
       <c r="A82" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C82" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E82" s="1">
         <v>1</v>
@@ -4367,30 +4320,30 @@
         <v>2</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="1:11">
       <c r="A83" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C83" s="1">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E83" s="1">
         <v>1</v>
@@ -4402,30 +4355,30 @@
         <v>2</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="J83" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="1:11">
       <c r="A84" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C84" s="1">
-        <v>124</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>225</v>
+        <v>123</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>221</v>
       </c>
       <c r="E84" s="1">
         <v>1</v>
@@ -4437,30 +4390,30 @@
         <v>2</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I84" s="5" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>225</v>
+        <v>85</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="1:11">
       <c r="A85" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C85" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E85" s="1">
         <v>1</v>
@@ -4472,30 +4425,30 @@
         <v>2</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I85" s="5" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="J85" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="1:11">
       <c r="A86" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C86" s="1">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E86" s="1">
         <v>1</v>
@@ -4507,30 +4460,30 @@
         <v>2</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="J86" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="1:11">
       <c r="A87" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C87" s="1">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E87" s="1">
         <v>1</v>
@@ -4542,100 +4495,100 @@
         <v>2</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I87" s="5" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="J87" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="1:11">
       <c r="A88" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C88" s="1">
+        <v>127</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E88" s="1">
+        <v>1</v>
+      </c>
+      <c r="F88" s="3">
+        <v>0</v>
+      </c>
+      <c r="G88" s="3">
+        <v>2</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="J88" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="1:11">
+      <c r="A89" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C89" s="1">
         <v>128</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E88" s="1">
-        <v>1</v>
-      </c>
-      <c r="F88" s="3">
-        <v>0</v>
-      </c>
-      <c r="G88" s="3">
-        <v>2</v>
-      </c>
-      <c r="H88" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="I88" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="J88" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K88" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="90" customHeight="1" spans="1:11">
-      <c r="A90" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C90" s="1">
-        <v>137</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="E90" s="1">
-        <v>1</v>
-      </c>
-      <c r="F90" s="3">
-        <v>0</v>
-      </c>
-      <c r="G90" s="3">
-        <v>2</v>
-      </c>
-      <c r="H90" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="I90" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="J90" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>235</v>
+      <c r="D89" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E89" s="1">
+        <v>1</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
+        <v>2</v>
+      </c>
+      <c r="H89" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="J89" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="1:11">
       <c r="A91" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C91" s="1">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E91" s="1">
         <v>1</v>
@@ -4647,88 +4600,94 @@
         <v>2</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>238</v>
+        <v>148</v>
       </c>
       <c r="I91" s="5" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="J91" s="5" t="s">
-        <v>240</v>
+        <v>39</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="1:11">
       <c r="A92" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C92" s="1">
+        <v>138</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E92" s="1">
+        <v>1</v>
+      </c>
+      <c r="F92" s="3">
+        <v>0</v>
+      </c>
+      <c r="G92" s="3">
+        <v>2</v>
+      </c>
+      <c r="H92" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="J92" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="1:11">
+      <c r="A93" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C93" s="1">
         <v>139</v>
       </c>
-      <c r="D92" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E92" s="1">
-        <v>1</v>
-      </c>
-      <c r="F92" s="3">
-        <v>0</v>
-      </c>
-      <c r="G92" s="3">
-        <v>2</v>
-      </c>
-      <c r="H92" s="5" t="s">
+      <c r="D93" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E93" s="1">
+        <v>1</v>
+      </c>
+      <c r="F93" s="3">
+        <v>0</v>
+      </c>
+      <c r="G93" s="3">
+        <v>2</v>
+      </c>
+      <c r="H93" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="I93" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="J93" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="I92" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="J92" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="102" customHeight="1" spans="3:11">
-      <c r="C102" s="1">
-        <v>201</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E102" s="1">
-        <v>1</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>2</v>
-      </c>
-      <c r="H102" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="I102" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="J102" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K102" s="1" t="s">
-        <v>246</v>
+      <c r="K93" s="1" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:11">
       <c r="C103" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="E103" s="1">
         <v>1</v>
@@ -4740,24 +4699,24 @@
         <v>2</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>244</v>
+        <v>34</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>248</v>
+        <v>35</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:11">
       <c r="C104" s="1">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="E104" s="1">
         <v>1</v>
@@ -4769,24 +4728,24 @@
         <v>2</v>
       </c>
       <c r="H104" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I104" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="I104" s="5" t="s">
-        <v>251</v>
-      </c>
       <c r="J104" s="5" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:11">
       <c r="C105" s="1">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E105" s="1">
         <v>1</v>
@@ -4798,24 +4757,24 @@
         <v>2</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>244</v>
+        <v>34</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:11">
       <c r="C106" s="1">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="E106" s="1">
         <v>1</v>
@@ -4827,24 +4786,24 @@
         <v>2</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>244</v>
+        <v>34</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="J106" s="5" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:11">
       <c r="C107" s="1">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="E107" s="1">
         <v>1</v>
@@ -4856,24 +4815,24 @@
         <v>2</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>244</v>
+        <v>34</v>
       </c>
       <c r="I107" s="5" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="J107" s="5" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:11">
       <c r="C108" s="1">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="E108" s="1">
         <v>1</v>
@@ -4885,24 +4844,24 @@
         <v>2</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>263</v>
+        <v>34</v>
       </c>
       <c r="I108" s="5" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="J108" s="5" t="s">
-        <v>265</v>
+        <v>16</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:11">
       <c r="C109" s="1">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="E109" s="1">
         <v>1</v>
@@ -4914,24 +4873,24 @@
         <v>2</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="I109" s="5" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="J109" s="5" t="s">
-        <v>141</v>
+        <v>261</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:11">
       <c r="C110" s="1">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E110" s="1">
         <v>1</v>
@@ -4943,45 +4902,74 @@
         <v>2</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="J110" s="5" t="s">
-        <v>265</v>
+        <v>139</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:11">
       <c r="C111" s="1">
+        <v>209</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E111" s="1">
+        <v>1</v>
+      </c>
+      <c r="F111" s="3">
+        <v>0</v>
+      </c>
+      <c r="G111" s="3">
+        <v>2</v>
+      </c>
+      <c r="H111" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="I111" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="J111" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="3:11">
+      <c r="C112" s="1">
         <v>210</v>
       </c>
-      <c r="D111" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E111" s="1">
-        <v>1</v>
-      </c>
-      <c r="F111" s="3">
-        <v>0</v>
-      </c>
-      <c r="G111" s="3">
-        <v>2</v>
-      </c>
-      <c r="H111" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="I111" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="J111" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="K111" s="1" t="s">
-        <v>273</v>
+      <c r="D112" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E112" s="1">
+        <v>1</v>
+      </c>
+      <c r="F112" s="3">
+        <v>0</v>
+      </c>
+      <c r="G112" s="3">
+        <v>2</v>
+      </c>
+      <c r="H112" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="I112" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="J112" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -5109,7 +5097,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -5121,16 +5109,16 @@
         <v>2</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5138,7 +5126,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -5150,16 +5138,16 @@
         <v>2</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5167,7 +5155,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -5179,16 +5167,16 @@
         <v>2</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5196,7 +5184,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -5208,16 +5196,16 @@
         <v>2</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5225,7 +5213,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -5237,16 +5225,16 @@
         <v>2</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5254,7 +5242,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -5266,16 +5254,16 @@
         <v>2</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5283,7 +5271,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -5295,16 +5283,16 @@
         <v>2</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5312,7 +5300,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -5324,16 +5312,16 @@
         <v>2</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5341,7 +5329,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -5353,16 +5341,16 @@
         <v>2</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5370,7 +5358,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -5382,16 +5370,16 @@
         <v>2</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5399,7 +5387,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -5411,16 +5399,16 @@
         <v>2</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5428,7 +5416,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -5440,16 +5428,16 @@
         <v>2</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5457,7 +5445,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -5469,16 +5457,16 @@
         <v>2</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5486,7 +5474,7 @@
         <v>1014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -5498,16 +5486,16 @@
         <v>2</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="18" customHeight="1"/>
@@ -5516,7 +5504,7 @@
         <v>1101</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -5528,16 +5516,16 @@
         <v>2</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5545,7 +5533,7 @@
         <v>1102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -5557,16 +5545,16 @@
         <v>2</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5574,7 +5562,7 @@
         <v>1103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -5586,16 +5574,16 @@
         <v>2</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5603,7 +5591,7 @@
         <v>1104</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -5615,16 +5603,16 @@
         <v>2</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5632,7 +5620,7 @@
         <v>1105</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -5644,16 +5632,16 @@
         <v>2</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5661,7 +5649,7 @@
         <v>1106</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -5673,16 +5661,16 @@
         <v>2</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5690,7 +5678,7 @@
         <v>1107</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -5702,16 +5690,16 @@
         <v>2</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5719,7 +5707,7 @@
         <v>1108</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -5731,16 +5719,16 @@
         <v>2</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5748,7 +5736,7 @@
         <v>1109</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -5760,16 +5748,16 @@
         <v>2</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5777,7 +5765,7 @@
         <v>1110</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -5789,16 +5777,16 @@
         <v>2</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5806,7 +5794,7 @@
         <v>1111</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -5818,16 +5806,16 @@
         <v>2</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5835,7 +5823,7 @@
         <v>1112</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -5847,16 +5835,16 @@
         <v>2</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -33,7 +33,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="E3" authorId="0">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -84,12 +84,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="347">
   <si>
     <t>_id</t>
   </si>
   <si>
     <t>Name</t>
+  </si>
+  <si>
+    <t>Quality</t>
   </si>
   <si>
     <t>GiftType</t>
@@ -2094,21 +2097,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:K112"/>
+  <dimension ref="A3:L112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="16.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.1666666666667" style="1" customWidth="1"/>
-    <col min="6" max="7" width="13.0833333333333" style="3" customWidth="1"/>
-    <col min="8" max="8" width="31.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="72.0166666666667" style="1" customWidth="1"/>
-    <col min="10" max="10" width="26.875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="42.25" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="4" max="5" width="16.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.1666666666667" style="1" customWidth="1"/>
+    <col min="7" max="8" width="13.0833333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="31.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="72.0166666666667" style="1" customWidth="1"/>
+    <col min="11" max="11" width="26.875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="42.25" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" customHeight="1" spans="3:11">
+    <row r="3" customHeight="1" spans="3:12">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2136,10 +2139,13 @@
       <c r="K3" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" customHeight="1" spans="3:11">
+      <c r="L3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="3:12">
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>1</v>
@@ -2165,54 +2171,60 @@
       <c r="K4" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" customHeight="1" spans="3:11">
+      <c r="L4" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="3:12">
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:11">
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>2</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>2</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>15</v>
@@ -2220,289 +2232,319 @@
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="1">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>2</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="5" t="s">
+      <c r="L7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>2</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>2</v>
       </c>
       <c r="I8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>2</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>2</v>
       </c>
       <c r="I9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E10" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>2</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>2</v>
       </c>
       <c r="I10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>2</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>2</v>
       </c>
       <c r="I11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>2</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>2</v>
       </c>
       <c r="I12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J12" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:11">
+    </row>
+    <row r="13" customHeight="1" spans="3:12">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E13" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>2</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>2</v>
       </c>
       <c r="I13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:11">
+    </row>
+    <row r="14" customHeight="1" spans="3:12">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>2</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>2</v>
       </c>
       <c r="I14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J14" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:11">
+    </row>
+    <row r="15" customHeight="1" spans="3:12">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E15" s="1">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
       </c>
       <c r="G15" s="3">
-        <v>2</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>34</v>
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>2</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>35</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:11">
+        <v>36</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:12">
       <c r="C17" s="1">
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E17" s="1">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="1">
-        <v>1</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>37</v>
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>38</v>
@@ -2510,57 +2552,57 @@
       <c r="J17" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="K17" s="5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:11">
+      <c r="L17" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:12">
       <c r="C18" s="1">
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E18" s="1">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1">
-        <v>1</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K18" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C19" s="1">
         <v>13</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="1">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>2</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>45</v>
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>2</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>46</v>
@@ -2568,289 +2610,289 @@
       <c r="J19" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="K19" s="5" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:11">
+      <c r="L19" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:12">
       <c r="C20" s="1">
         <v>14</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E20" s="1">
-        <v>1</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="1">
-        <v>2</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>2</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="K20" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:11">
+      <c r="K20" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:12">
       <c r="C21" s="1">
         <v>15</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E21" s="1">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
-      <c r="G21" s="1">
-        <v>1</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>37</v>
+        <v>53</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K21" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:11">
+      <c r="K21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:12">
       <c r="C22" s="1">
         <v>16</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E22" s="1">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>37</v>
+        <v>56</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K22" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:11">
+      <c r="K22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:12">
       <c r="C23" s="1">
         <v>17</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E23" s="1">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
-      <c r="G23" s="1">
-        <v>1</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>37</v>
+        <v>59</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K23" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:11">
+      <c r="K23" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:12">
       <c r="C24" s="1">
         <v>18</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" s="1">
-        <v>1</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="1">
-        <v>2</v>
-      </c>
-      <c r="H24" s="5" t="s">
         <v>62</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>2</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>63</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K24" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:11">
+      <c r="K24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:12">
       <c r="C25" s="1">
         <v>19</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E25" s="1">
-        <v>1</v>
-      </c>
-      <c r="F25" s="3">
-        <v>0</v>
-      </c>
-      <c r="G25" s="1">
-        <v>2</v>
-      </c>
-      <c r="H25" s="5" t="s">
         <v>66</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>2</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>67</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:11">
+        <v>68</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:12">
       <c r="C26" s="1">
         <v>20</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E26" s="1">
-        <v>1</v>
-      </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
-      <c r="G26" s="1">
-        <v>2</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>66</v>
+        <v>69</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>2</v>
       </c>
       <c r="I26" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J26" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:11">
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C27" s="1">
         <v>21</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E27" s="1">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="F27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="1">
-        <v>2</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>71</v>
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>2</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>72</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K27" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K27" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C28" s="1">
         <v>22</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E28" s="1">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="F28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="1">
-        <v>2</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>75</v>
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>2</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>76</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:11">
+        <v>77</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:12">
       <c r="C29" s="1">
         <v>23</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E29" s="1">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="F29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="1">
-        <v>2</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>78</v>
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>2</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>79</v>
@@ -2858,57 +2900,57 @@
       <c r="J29" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:11">
+      <c r="K29" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:12">
       <c r="C30" s="1">
         <v>24</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E30" s="1">
-        <v>1</v>
-      </c>
-      <c r="F30" s="3">
-        <v>0</v>
-      </c>
-      <c r="G30" s="1">
-        <v>2</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>62</v>
+        <v>82</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1</v>
+      </c>
+      <c r="G30" s="3">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>2</v>
       </c>
       <c r="I30" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L30" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="J30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:11">
+    </row>
+    <row r="31" customHeight="1" spans="3:12">
       <c r="C31" s="1">
         <v>25</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E31" s="1">
-        <v>1</v>
-      </c>
-      <c r="F31" s="3">
-        <v>0</v>
-      </c>
-      <c r="G31" s="1">
-        <v>2</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>83</v>
+        <v>62</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1</v>
+      </c>
+      <c r="G31" s="3">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>2</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>84</v>
@@ -2916,28 +2958,28 @@
       <c r="J31" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:11">
+      <c r="K31" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:12">
       <c r="C32" s="1">
         <v>26</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E32" s="1">
-        <v>1</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="1">
-        <v>2</v>
-      </c>
-      <c r="H32" s="5" t="s">
         <v>87</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>2</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>88</v>
@@ -2945,115 +2987,115 @@
       <c r="J32" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="1:11">
+      <c r="K32" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:12">
       <c r="C33" s="1">
         <v>27</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E33" s="1">
-        <v>1</v>
-      </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
-      <c r="G33" s="1">
-        <v>2</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>14</v>
+        <v>91</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1</v>
+      </c>
+      <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>2</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K33" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="34" customHeight="1" spans="1:11">
+      <c r="K33" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:12">
       <c r="C34" s="1">
         <v>28</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E34" s="1">
-        <v>1</v>
-      </c>
-      <c r="F34" s="3">
-        <v>0</v>
-      </c>
-      <c r="G34" s="1">
-        <v>2</v>
-      </c>
-      <c r="H34" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="I34" s="6" t="s">
+      <c r="F34" s="1">
+        <v>1</v>
+      </c>
+      <c r="G34" s="3">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
+        <v>2</v>
+      </c>
+      <c r="I34" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="J34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="1:11">
+      <c r="J34" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:12">
       <c r="C35" s="1">
         <v>29</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E35" s="1">
-        <v>1</v>
-      </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
-      <c r="G35" s="1">
-        <v>2</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>14</v>
+        <v>97</v>
+      </c>
+      <c r="F35" s="1">
+        <v>1</v>
+      </c>
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>2</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K35" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="36" customHeight="1" spans="1:11">
+      <c r="K35" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:12">
       <c r="C36" s="1">
         <v>30</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E36" s="1">
-        <v>1</v>
-      </c>
-      <c r="F36" s="3">
-        <v>0</v>
-      </c>
-      <c r="G36" s="1">
-        <v>2</v>
-      </c>
-      <c r="H36" s="5" t="s">
         <v>100</v>
+      </c>
+      <c r="F36" s="1">
+        <v>1</v>
+      </c>
+      <c r="G36" s="3">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1">
+        <v>2</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>101</v>
@@ -3061,57 +3103,57 @@
       <c r="J36" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="K36" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="1:11">
+      <c r="K36" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:12">
       <c r="C37" s="1">
         <v>31</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E37" s="1">
-        <v>1</v>
-      </c>
-      <c r="F37" s="3">
-        <v>0</v>
-      </c>
-      <c r="G37" s="1">
-        <v>2</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>62</v>
+        <v>104</v>
+      </c>
+      <c r="F37" s="1">
+        <v>1</v>
+      </c>
+      <c r="G37" s="3">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>2</v>
       </c>
       <c r="I37" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L37" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="J37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="1:11">
+    </row>
+    <row r="38" customHeight="1" spans="1:12">
       <c r="C38" s="1">
         <v>32</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E38" s="1">
-        <v>0</v>
-      </c>
-      <c r="F38" s="3">
-        <v>0</v>
-      </c>
-      <c r="G38" s="1">
-        <v>2</v>
-      </c>
-      <c r="H38" s="5" t="s">
         <v>106</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>2</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>107</v>
@@ -3119,117 +3161,118 @@
       <c r="J38" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="K38" s="5" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="39" customHeight="1" spans="1:11">
+      <c r="L38" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:12">
       <c r="C39" s="1">
         <v>33</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E39" s="1">
-        <v>0</v>
-      </c>
-      <c r="F39" s="3">
-        <v>0</v>
-      </c>
-      <c r="G39" s="1">
-        <v>2</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>106</v>
+        <v>111</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>2</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J39" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="K39" s="5" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="40" customFormat="1" customHeight="1" spans="1:11">
+      <c r="L39" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" customHeight="1" spans="1:12">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1">
         <v>34</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E40" s="1">
-        <v>1</v>
-      </c>
-      <c r="F40" s="3">
-        <v>0</v>
-      </c>
-      <c r="G40">
-        <v>2</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>62</v>
+        <v>115</v>
+      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1">
+        <v>1</v>
+      </c>
+      <c r="G40" s="3">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>2</v>
       </c>
       <c r="I40" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L40" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="J40" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="1:11">
+    </row>
+    <row r="41" customHeight="1" spans="1:12">
       <c r="C41" s="1">
         <v>35</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E41" s="1">
-        <v>1</v>
-      </c>
-      <c r="F41" s="3">
-        <v>0</v>
-      </c>
-      <c r="G41" s="1">
-        <v>1</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>87</v>
+        <v>117</v>
+      </c>
+      <c r="F41" s="1">
+        <v>1</v>
+      </c>
+      <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1</v>
       </c>
       <c r="I41" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="L41" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="J41" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="1:11">
+    </row>
+    <row r="42" customHeight="1" spans="1:12">
       <c r="C42" s="1">
         <v>36</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E42" s="1">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
+        <v>119</v>
+      </c>
+      <c r="F42" s="1">
         <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>1</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>119</v>
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>1</v>
       </c>
       <c r="I42" s="5" t="s">
         <v>120</v>
@@ -3237,204 +3280,205 @@
       <c r="J42" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="K42" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="1:11">
+      <c r="K42" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="1:12">
       <c r="C43" s="1">
         <v>37</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E43" s="1">
-        <v>1</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="1">
-        <v>1</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>87</v>
+        <v>123</v>
+      </c>
+      <c r="F43" s="1">
+        <v>1</v>
+      </c>
+      <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
+        <v>1</v>
       </c>
       <c r="I43" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="L43" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="J43" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="1:11">
+    </row>
+    <row r="44" customHeight="1" spans="1:12">
       <c r="C44" s="1">
         <v>38</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E44" s="1">
-        <v>1</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="1">
-        <v>1</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>87</v>
+        <v>125</v>
+      </c>
+      <c r="F44" s="1">
+        <v>1</v>
+      </c>
+      <c r="G44" s="3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>1</v>
       </c>
       <c r="I44" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="L44" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="J44" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="1:11">
+    </row>
+    <row r="45" customHeight="1" spans="1:12">
       <c r="C45" s="1">
         <v>39</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E45" s="1">
-        <v>1</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="1">
-        <v>1</v>
-      </c>
-      <c r="H45" s="5" t="s">
-        <v>87</v>
+        <v>127</v>
+      </c>
+      <c r="F45" s="1">
+        <v>1</v>
+      </c>
+      <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>1</v>
       </c>
       <c r="I45" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="L45" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J45" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="1:11">
+    </row>
+    <row r="46" customHeight="1" spans="1:12">
       <c r="C46" s="1">
         <v>40</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E46" s="1">
-        <v>1</v>
-      </c>
-      <c r="F46" s="3">
-        <v>0</v>
-      </c>
-      <c r="G46" s="1">
-        <v>1</v>
-      </c>
-      <c r="H46" s="5" t="s">
-        <v>87</v>
+        <v>129</v>
+      </c>
+      <c r="F46" s="1">
+        <v>1</v>
+      </c>
+      <c r="G46" s="3">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1">
+        <v>1</v>
       </c>
       <c r="I46" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="L46" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="J46" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="1:11">
+    </row>
+    <row r="47" customHeight="1" spans="1:12">
       <c r="C47" s="1">
         <v>41</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E47" s="1">
-        <v>1</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="1">
-        <v>1</v>
-      </c>
-      <c r="H47" s="5" t="s">
         <v>131</v>
+      </c>
+      <c r="F47" s="1">
+        <v>1</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
+        <v>1</v>
       </c>
       <c r="I47" s="5" t="s">
         <v>132</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="1:11">
+        <v>133</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="1:12">
       <c r="C48" s="1">
         <v>42</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E48" s="1">
-        <v>1</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="1">
-        <v>2</v>
-      </c>
-      <c r="H48" s="5" t="s">
-        <v>14</v>
+        <v>134</v>
+      </c>
+      <c r="F48" s="1">
+        <v>1</v>
+      </c>
+      <c r="G48" s="3">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
+        <v>2</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K48" s="1" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="49" customFormat="1" customHeight="1" spans="1:11">
+      <c r="K48" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="1:12">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1">
         <v>43</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E49" s="1">
-        <v>1</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
+        <v>137</v>
+      </c>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1">
+        <v>1</v>
       </c>
       <c r="G49" s="3">
-        <v>2</v>
-      </c>
-      <c r="H49" s="5" t="s">
-        <v>137</v>
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>2</v>
       </c>
       <c r="I49" s="5" t="s">
         <v>138</v>
@@ -3442,194 +3486,199 @@
       <c r="J49" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="K49" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="50" s="1" customFormat="1" customHeight="1" spans="1:11">
+      <c r="K49" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C50" s="1">
         <v>44</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E50" s="1">
-        <v>1</v>
+        <v>141</v>
       </c>
       <c r="F50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" s="1">
-        <v>2</v>
-      </c>
-      <c r="H50" s="5" t="s">
-        <v>75</v>
+        <v>0</v>
+      </c>
+      <c r="H50" s="1">
+        <v>2</v>
       </c>
       <c r="I50" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L50" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="J50" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="51" customFormat="1" customHeight="1" spans="1:11">
+    </row>
+    <row r="51" customFormat="1" customHeight="1" spans="1:12">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
-      <c r="F51" s="3"/>
+      <c r="F51" s="1"/>
       <c r="G51" s="3"/>
-      <c r="H51" s="1"/>
+      <c r="H51" s="3"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
-    </row>
-    <row r="52" customFormat="1" customHeight="1" spans="1:11">
+      <c r="L51" s="1"/>
+    </row>
+    <row r="52" customFormat="1" customHeight="1" spans="1:12">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1">
         <v>90</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E52" s="1">
-        <v>1</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="1">
-        <v>2</v>
-      </c>
-      <c r="H52" s="5" t="s">
         <v>143</v>
+      </c>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1">
+        <v>1</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>2</v>
       </c>
       <c r="I52" s="5" t="s">
         <v>144</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="53" customFormat="1" customHeight="1" spans="1:11">
+        <v>145</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" customHeight="1" spans="1:12">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1">
         <v>91</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E53" s="1">
-        <v>1</v>
-      </c>
-      <c r="F53" s="3">
-        <v>0</v>
-      </c>
-      <c r="G53" s="1">
-        <v>2</v>
-      </c>
-      <c r="H53" s="5" t="s">
-        <v>131</v>
+        <v>146</v>
+      </c>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1">
+        <v>1</v>
+      </c>
+      <c r="G53" s="3">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>2</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="54" customFormat="1" customHeight="1" spans="1:11">
+        <v>147</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" customHeight="1" spans="1:12">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1">
         <v>94</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E54" s="1">
-        <v>1</v>
-      </c>
-      <c r="F54" s="3">
-        <v>0</v>
-      </c>
-      <c r="G54" s="1">
-        <v>2</v>
-      </c>
-      <c r="H54" s="5" t="s">
         <v>148</v>
+      </c>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1">
+        <v>1</v>
+      </c>
+      <c r="G54" s="3">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1">
+        <v>2</v>
       </c>
       <c r="I54" s="5" t="s">
         <v>149</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="55" customFormat="1" customHeight="1" spans="1:11">
+        <v>150</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" customHeight="1" spans="1:12">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1">
         <v>95</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E55" s="1">
-        <v>1</v>
-      </c>
-      <c r="F55" s="3">
-        <v>0</v>
-      </c>
-      <c r="G55" s="1">
-        <v>2</v>
-      </c>
-      <c r="H55" s="5" t="s">
-        <v>143</v>
+        <v>151</v>
+      </c>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1">
+        <v>1</v>
+      </c>
+      <c r="G55" s="3">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1">
+        <v>2</v>
       </c>
       <c r="I55" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="L55" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="J55" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="1:11">
+    </row>
+    <row r="56" customHeight="1" spans="1:12">
       <c r="C56" s="1">
         <v>96</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E56" s="1">
-        <v>0</v>
-      </c>
-      <c r="F56" s="3">
-        <v>0</v>
-      </c>
-      <c r="G56" s="1">
-        <v>2</v>
-      </c>
-      <c r="H56" s="5" t="s">
         <v>153</v>
+      </c>
+      <c r="F56" s="1">
+        <v>0</v>
+      </c>
+      <c r="G56" s="3">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1">
+        <v>2</v>
       </c>
       <c r="I56" s="5" t="s">
         <v>154</v>
@@ -3637,86 +3686,86 @@
       <c r="J56" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="K56" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="1:11">
+      <c r="K56" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="1:12">
       <c r="C57" s="1">
         <v>97</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E57" s="1">
-        <v>1</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1">
-        <v>2</v>
-      </c>
-      <c r="H57" s="5" t="s">
         <v>157</v>
+      </c>
+      <c r="F57" s="1">
+        <v>1</v>
+      </c>
+      <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1">
+        <v>2</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>158</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="1:11">
+        <v>159</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="1:12">
       <c r="C58" s="1">
         <v>98</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E58" s="1">
-        <v>1</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="1">
-        <v>2</v>
-      </c>
-      <c r="H58" s="5" t="s">
         <v>160</v>
+      </c>
+      <c r="F58" s="1">
+        <v>1</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <v>2</v>
       </c>
       <c r="I58" s="5" t="s">
         <v>161</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="1:11">
+        <v>162</v>
+      </c>
+      <c r="K58" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="1:12">
       <c r="C59" s="1">
         <v>99</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E59" s="1">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1">
-        <v>2</v>
-      </c>
-      <c r="H59" s="5" t="s">
         <v>163</v>
+      </c>
+      <c r="F59" s="1">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1">
+        <v>2</v>
       </c>
       <c r="I59" s="5" t="s">
         <v>164</v>
@@ -3724,202 +3773,202 @@
       <c r="J59" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="K59" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="1:11">
+      <c r="K59" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="1:12">
       <c r="C60" s="1">
         <v>100</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E60" s="1">
-        <v>0</v>
-      </c>
-      <c r="F60" s="3">
-        <v>0</v>
-      </c>
-      <c r="G60" s="1">
-        <v>2</v>
-      </c>
-      <c r="H60" s="5" t="s">
-        <v>153</v>
+        <v>167</v>
+      </c>
+      <c r="F60" s="1">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>2</v>
       </c>
       <c r="I60" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="K60" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="L60" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="J60" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="1:11">
+    </row>
+    <row r="61" customHeight="1" spans="1:12">
       <c r="C61" s="1">
         <v>101</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E61" s="1">
-        <v>0</v>
-      </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
-      <c r="G61" s="1">
-        <v>2</v>
-      </c>
-      <c r="H61" s="5" t="s">
-        <v>153</v>
+        <v>169</v>
+      </c>
+      <c r="F61" s="1">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1">
+        <v>2</v>
       </c>
       <c r="I61" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="K61" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="L61" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="J61" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="1:11">
+    </row>
+    <row r="62" customHeight="1" spans="1:12">
       <c r="C62" s="1">
         <v>102</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="E62" s="1">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="1">
-        <v>2</v>
-      </c>
-      <c r="H62" s="5" t="s">
-        <v>163</v>
+        <v>171</v>
+      </c>
+      <c r="F62" s="1">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1">
+        <v>2</v>
       </c>
       <c r="I62" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="J62" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="K62" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L62" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="J62" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="63" customHeight="1" spans="1:11">
+    </row>
+    <row r="63" customHeight="1" spans="1:12">
       <c r="C63" s="1">
         <v>103</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E63" s="1">
-        <v>0</v>
-      </c>
-      <c r="F63" s="3">
-        <v>0</v>
-      </c>
-      <c r="G63" s="1">
-        <v>2</v>
-      </c>
-      <c r="H63" s="5" t="s">
-        <v>163</v>
+        <v>173</v>
+      </c>
+      <c r="F63" s="1">
+        <v>0</v>
+      </c>
+      <c r="G63" s="3">
+        <v>0</v>
+      </c>
+      <c r="H63" s="1">
+        <v>2</v>
       </c>
       <c r="I63" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="K63" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L63" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="J63" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="1:11">
+    </row>
+    <row r="64" customHeight="1" spans="1:12">
       <c r="C64" s="1">
         <v>104</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E64" s="1">
-        <v>0</v>
-      </c>
-      <c r="F64" s="3">
-        <v>0</v>
-      </c>
-      <c r="G64" s="1">
-        <v>2</v>
-      </c>
-      <c r="H64" s="5" t="s">
-        <v>163</v>
+        <v>175</v>
+      </c>
+      <c r="F64" s="1">
+        <v>0</v>
+      </c>
+      <c r="G64" s="3">
+        <v>0</v>
+      </c>
+      <c r="H64" s="1">
+        <v>2</v>
       </c>
       <c r="I64" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="K64" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L64" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="J64" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="1:11">
+    </row>
+    <row r="65" customHeight="1" spans="1:12">
       <c r="C65" s="1">
         <v>105</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="E65" s="1">
-        <v>0</v>
-      </c>
-      <c r="F65" s="3">
-        <v>0</v>
-      </c>
-      <c r="G65" s="1">
-        <v>2</v>
-      </c>
-      <c r="H65" s="5" t="s">
-        <v>163</v>
+        <v>177</v>
+      </c>
+      <c r="F65" s="1">
+        <v>0</v>
+      </c>
+      <c r="G65" s="3">
+        <v>0</v>
+      </c>
+      <c r="H65" s="1">
+        <v>2</v>
       </c>
       <c r="I65" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="J65" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="K65" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L65" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="J65" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="1:11">
+    </row>
+    <row r="67" customHeight="1" spans="1:12">
       <c r="C67" s="1">
         <v>106</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E67" s="1">
-        <v>1</v>
-      </c>
-      <c r="F67" s="3">
-        <v>0</v>
-      </c>
-      <c r="G67" s="1">
-        <v>1</v>
-      </c>
-      <c r="H67" s="5" t="s">
         <v>179</v>
+      </c>
+      <c r="F67" s="1">
+        <v>1</v>
+      </c>
+      <c r="G67" s="3">
+        <v>0</v>
+      </c>
+      <c r="H67" s="1">
+        <v>1</v>
       </c>
       <c r="I67" s="5" t="s">
         <v>180</v>
@@ -3927,715 +3976,721 @@
       <c r="J67" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="K67" s="1" t="s">
+      <c r="K67" s="5" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="68" customHeight="1" spans="1:11">
+      <c r="L67" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="1:12">
       <c r="C68" s="1">
         <v>107</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E68" s="1">
-        <v>1</v>
-      </c>
-      <c r="F68" s="3">
-        <v>0</v>
-      </c>
-      <c r="G68" s="1">
-        <v>2</v>
-      </c>
-      <c r="H68" s="5" t="s">
-        <v>62</v>
+        <v>184</v>
+      </c>
+      <c r="F68" s="1">
+        <v>1</v>
+      </c>
+      <c r="G68" s="3">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1">
+        <v>2</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>184</v>
+        <v>63</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="69" customHeight="1" spans="1:11">
+        <v>185</v>
+      </c>
+      <c r="K68" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="1:12">
       <c r="C69" s="1">
         <v>108</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="E69" s="1">
-        <v>1</v>
-      </c>
-      <c r="F69" s="3">
-        <v>0</v>
-      </c>
-      <c r="G69" s="1">
-        <v>2</v>
-      </c>
-      <c r="H69" s="5" t="s">
-        <v>62</v>
+        <v>186</v>
+      </c>
+      <c r="F69" s="1">
+        <v>1</v>
+      </c>
+      <c r="G69" s="3">
+        <v>0</v>
+      </c>
+      <c r="H69" s="1">
+        <v>2</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>186</v>
+        <v>63</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K69" s="1" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="71" customHeight="1" spans="1:11">
+      <c r="K69" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="1:12">
       <c r="C71" s="1">
         <v>109</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E71" s="1">
-        <v>1</v>
-      </c>
-      <c r="F71" s="3">
-        <v>0</v>
+        <v>189</v>
+      </c>
+      <c r="F71" s="1">
+        <v>1</v>
       </c>
       <c r="G71" s="3">
-        <v>2</v>
-      </c>
-      <c r="H71" s="5" t="s">
-        <v>189</v>
+        <v>0</v>
+      </c>
+      <c r="H71" s="3">
+        <v>2</v>
       </c>
       <c r="I71" s="5" t="s">
         <v>190</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K71" s="1" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="72" customHeight="1" spans="1:11">
+      <c r="K71" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="1:12">
       <c r="C72" s="1">
         <v>110</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="E72" s="1">
-        <v>1</v>
-      </c>
-      <c r="F72" s="3">
-        <v>0</v>
+        <v>193</v>
+      </c>
+      <c r="F72" s="1">
+        <v>1</v>
       </c>
       <c r="G72" s="3">
-        <v>2</v>
-      </c>
-      <c r="H72" s="5" t="s">
-        <v>189</v>
+        <v>0</v>
+      </c>
+      <c r="H72" s="3">
+        <v>2</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K72" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="73" customHeight="1" spans="1:11">
+      <c r="K72" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="1:12">
       <c r="C73" s="1">
         <v>111</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="E73" s="1">
-        <v>1</v>
-      </c>
-      <c r="F73" s="3">
-        <v>0</v>
+        <v>196</v>
+      </c>
+      <c r="F73" s="1">
+        <v>1</v>
       </c>
       <c r="G73" s="3">
-        <v>2</v>
-      </c>
-      <c r="H73" s="5" t="s">
-        <v>189</v>
+        <v>0</v>
+      </c>
+      <c r="H73" s="3">
+        <v>2</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K73" s="1" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="74" customHeight="1" spans="1:11">
+      <c r="K73" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="1:12">
       <c r="C74" s="1">
         <v>112</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="E74" s="1">
-        <v>1</v>
-      </c>
-      <c r="F74" s="3">
-        <v>0</v>
+        <v>199</v>
+      </c>
+      <c r="F74" s="1">
+        <v>1</v>
       </c>
       <c r="G74" s="3">
-        <v>2</v>
-      </c>
-      <c r="H74" s="5" t="s">
-        <v>189</v>
+        <v>0</v>
+      </c>
+      <c r="H74" s="3">
+        <v>2</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K74" s="1" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="75" customHeight="1" spans="1:11">
+      <c r="K74" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="1:12">
       <c r="C75" s="1">
         <v>113</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E75" s="1">
-        <v>1</v>
-      </c>
-      <c r="F75" s="3">
-        <v>0</v>
+        <v>202</v>
+      </c>
+      <c r="F75" s="1">
+        <v>1</v>
       </c>
       <c r="G75" s="3">
-        <v>2</v>
-      </c>
-      <c r="H75" s="5" t="s">
-        <v>189</v>
+        <v>0</v>
+      </c>
+      <c r="H75" s="3">
+        <v>2</v>
       </c>
       <c r="I75" s="5" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K75" s="1" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="76" customHeight="1" spans="1:11">
+      <c r="K75" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="1:12">
       <c r="C76" s="1">
         <v>114</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="E76" s="1">
-        <v>1</v>
-      </c>
-      <c r="F76" s="3">
-        <v>0</v>
+        <v>205</v>
+      </c>
+      <c r="F76" s="1">
+        <v>1</v>
       </c>
       <c r="G76" s="3">
-        <v>2</v>
-      </c>
-      <c r="H76" s="5" t="s">
-        <v>205</v>
+        <v>0</v>
+      </c>
+      <c r="H76" s="3">
+        <v>2</v>
       </c>
       <c r="I76" s="5" t="s">
         <v>206</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="K76" s="1" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="77" customHeight="1" spans="1:11">
+      <c r="K76" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="1:12">
       <c r="C77" s="1">
         <v>115</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="E77" s="1">
-        <v>1</v>
-      </c>
-      <c r="F77" s="3">
-        <v>0</v>
+        <v>209</v>
+      </c>
+      <c r="F77" s="1">
+        <v>1</v>
       </c>
       <c r="G77" s="3">
-        <v>2</v>
-      </c>
-      <c r="H77" s="5" t="s">
-        <v>148</v>
+        <v>0</v>
+      </c>
+      <c r="H77" s="3">
+        <v>2</v>
       </c>
       <c r="I77" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="J77" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="K77" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L77" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="J77" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="79" customHeight="1" spans="1:11">
+    </row>
+    <row r="79" customHeight="1" spans="1:12">
       <c r="A79" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C79" s="1">
         <v>118</v>
       </c>
       <c r="D79" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E79" s="3"/>
+      <c r="F79" s="1">
+        <v>1</v>
+      </c>
+      <c r="G79" s="3">
+        <v>0</v>
+      </c>
+      <c r="H79" s="3">
+        <v>2</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J79" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K79" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="1:12">
+      <c r="A80" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E79" s="1">
-        <v>1</v>
-      </c>
-      <c r="F79" s="3">
-        <v>0</v>
-      </c>
-      <c r="G79" s="3">
-        <v>2</v>
-      </c>
-      <c r="H79" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="I79" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="J79" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K79" s="3" t="s">
+      <c r="B80" s="1" t="s">
         <v>211</v>
-      </c>
-    </row>
-    <row r="80" customHeight="1" spans="1:11">
-      <c r="A80" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="C80" s="1">
         <v>119</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E80" s="1">
-        <v>1</v>
-      </c>
-      <c r="F80" s="3">
-        <v>0</v>
+        <v>214</v>
+      </c>
+      <c r="E80" s="3"/>
+      <c r="F80" s="1">
+        <v>1</v>
       </c>
       <c r="G80" s="3">
-        <v>2</v>
-      </c>
-      <c r="H80" s="5" t="s">
-        <v>189</v>
+        <v>0</v>
+      </c>
+      <c r="H80" s="3">
+        <v>2</v>
       </c>
       <c r="I80" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J80" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="K80" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L80" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="J80" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K80" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="81" customHeight="1" spans="1:11">
+    </row>
+    <row r="81" customHeight="1" spans="1:12">
       <c r="A81" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C81" s="1">
         <v>120</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E81" s="1">
-        <v>1</v>
-      </c>
-      <c r="F81" s="3">
-        <v>0</v>
+        <v>216</v>
+      </c>
+      <c r="E81" s="3"/>
+      <c r="F81" s="1">
+        <v>1</v>
       </c>
       <c r="G81" s="3">
-        <v>2</v>
-      </c>
-      <c r="H81" s="5" t="s">
-        <v>189</v>
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
+        <v>2</v>
       </c>
       <c r="I81" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J81" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="K81" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L81" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="J81" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="82" customHeight="1" spans="1:11">
+    </row>
+    <row r="82" customHeight="1" spans="1:12">
       <c r="A82" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C82" s="1">
         <v>121</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E82" s="1">
-        <v>1</v>
-      </c>
-      <c r="F82" s="3">
-        <v>0</v>
+        <v>218</v>
+      </c>
+      <c r="E82" s="3"/>
+      <c r="F82" s="1">
+        <v>1</v>
       </c>
       <c r="G82" s="3">
-        <v>2</v>
-      </c>
-      <c r="H82" s="5" t="s">
-        <v>189</v>
+        <v>0</v>
+      </c>
+      <c r="H82" s="3">
+        <v>2</v>
       </c>
       <c r="I82" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J82" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="K82" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L82" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="J82" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K82" s="3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="83" customHeight="1" spans="1:11">
+    </row>
+    <row r="83" customHeight="1" spans="1:12">
       <c r="A83" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C83" s="1">
         <v>122</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="E83" s="1">
-        <v>1</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
+        <v>220</v>
+      </c>
+      <c r="E83" s="3"/>
+      <c r="F83" s="1">
+        <v>1</v>
       </c>
       <c r="G83" s="3">
-        <v>2</v>
-      </c>
-      <c r="H83" s="5" t="s">
-        <v>189</v>
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>2</v>
       </c>
       <c r="I83" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J83" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="K83" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L83" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="J83" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="84" customHeight="1" spans="1:11">
+    </row>
+    <row r="84" customHeight="1" spans="1:12">
       <c r="A84" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C84" s="1">
         <v>123</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E84" s="1">
-        <v>1</v>
-      </c>
-      <c r="F84" s="3">
-        <v>0</v>
+        <v>222</v>
+      </c>
+      <c r="E84" s="3"/>
+      <c r="F84" s="1">
+        <v>1</v>
       </c>
       <c r="G84" s="3">
-        <v>2</v>
-      </c>
-      <c r="H84" s="5" t="s">
-        <v>189</v>
+        <v>0</v>
+      </c>
+      <c r="H84" s="3">
+        <v>2</v>
       </c>
       <c r="I84" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J84" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="K84" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L84" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="J84" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K84" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="85" customHeight="1" spans="1:11">
+    </row>
+    <row r="85" customHeight="1" spans="1:12">
       <c r="A85" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C85" s="1">
         <v>124</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="E85" s="1">
-        <v>1</v>
-      </c>
-      <c r="F85" s="3">
-        <v>0</v>
+        <v>224</v>
+      </c>
+      <c r="F85" s="1">
+        <v>1</v>
       </c>
       <c r="G85" s="3">
-        <v>2</v>
-      </c>
-      <c r="H85" s="5" t="s">
-        <v>189</v>
+        <v>0</v>
+      </c>
+      <c r="H85" s="3">
+        <v>2</v>
       </c>
       <c r="I85" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J85" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="K85" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L85" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="J85" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K85" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="86" customHeight="1" spans="1:11">
+    </row>
+    <row r="86" customHeight="1" spans="1:12">
       <c r="A86" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C86" s="1">
         <v>125</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="E86" s="1">
-        <v>1</v>
-      </c>
-      <c r="F86" s="3">
-        <v>0</v>
+        <v>226</v>
+      </c>
+      <c r="F86" s="1">
+        <v>1</v>
       </c>
       <c r="G86" s="3">
-        <v>2</v>
-      </c>
-      <c r="H86" s="5" t="s">
-        <v>189</v>
+        <v>0</v>
+      </c>
+      <c r="H86" s="3">
+        <v>2</v>
       </c>
       <c r="I86" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J86" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="K86" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L86" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="J86" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K86" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="87" customHeight="1" spans="1:11">
+    </row>
+    <row r="87" customHeight="1" spans="1:12">
       <c r="A87" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C87" s="1">
         <v>126</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="E87" s="1">
-        <v>1</v>
-      </c>
-      <c r="F87" s="3">
-        <v>0</v>
+        <v>228</v>
+      </c>
+      <c r="F87" s="1">
+        <v>1</v>
       </c>
       <c r="G87" s="3">
-        <v>2</v>
-      </c>
-      <c r="H87" s="5" t="s">
-        <v>189</v>
+        <v>0</v>
+      </c>
+      <c r="H87" s="3">
+        <v>2</v>
       </c>
       <c r="I87" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J87" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="K87" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L87" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="J87" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K87" s="1" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="88" customHeight="1" spans="1:11">
+    </row>
+    <row r="88" customHeight="1" spans="1:12">
       <c r="A88" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C88" s="1">
         <v>127</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E88" s="1">
-        <v>1</v>
-      </c>
-      <c r="F88" s="3">
-        <v>0</v>
+        <v>230</v>
+      </c>
+      <c r="F88" s="1">
+        <v>1</v>
       </c>
       <c r="G88" s="3">
-        <v>2</v>
-      </c>
-      <c r="H88" s="5" t="s">
-        <v>189</v>
+        <v>0</v>
+      </c>
+      <c r="H88" s="3">
+        <v>2</v>
       </c>
       <c r="I88" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J88" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="K88" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L88" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="J88" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K88" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="89" customHeight="1" spans="1:11">
+    </row>
+    <row r="89" customHeight="1" spans="1:12">
       <c r="A89" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C89" s="1">
         <v>128</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E89" s="1">
-        <v>1</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
+        <v>232</v>
+      </c>
+      <c r="F89" s="1">
+        <v>1</v>
       </c>
       <c r="G89" s="3">
-        <v>2</v>
-      </c>
-      <c r="H89" s="5" t="s">
-        <v>189</v>
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
+        <v>2</v>
       </c>
       <c r="I89" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J89" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="K89" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L89" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="J89" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K89" s="1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="91" customHeight="1" spans="1:11">
+    </row>
+    <row r="91" customHeight="1" spans="1:12">
       <c r="A91" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C91" s="1">
         <v>137</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E91" s="1">
-        <v>1</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
+        <v>234</v>
+      </c>
+      <c r="F91" s="1">
+        <v>1</v>
       </c>
       <c r="G91" s="3">
-        <v>2</v>
-      </c>
-      <c r="H91" s="5" t="s">
-        <v>148</v>
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
+        <v>2</v>
       </c>
       <c r="I91" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="J91" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="K91" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L91" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="J91" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="92" customHeight="1" spans="1:11">
+    </row>
+    <row r="92" customHeight="1" spans="1:12">
       <c r="A92" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C92" s="1">
         <v>138</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="E92" s="1">
-        <v>1</v>
-      </c>
-      <c r="F92" s="3">
-        <v>0</v>
+        <v>236</v>
+      </c>
+      <c r="F92" s="1">
+        <v>1</v>
       </c>
       <c r="G92" s="3">
-        <v>2</v>
-      </c>
-      <c r="H92" s="5" t="s">
-        <v>236</v>
+        <v>0</v>
+      </c>
+      <c r="H92" s="3">
+        <v>2</v>
       </c>
       <c r="I92" s="5" t="s">
         <v>237</v>
@@ -4643,237 +4698,237 @@
       <c r="J92" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="K92" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="93" customHeight="1" spans="1:11">
+      <c r="K92" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="1:12">
       <c r="A93" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C93" s="1">
         <v>139</v>
       </c>
       <c r="D93" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F93" s="1">
+        <v>1</v>
+      </c>
+      <c r="G93" s="3">
+        <v>0</v>
+      </c>
+      <c r="H93" s="3">
+        <v>2</v>
+      </c>
+      <c r="I93" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="J93" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="K93" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="E93" s="1">
-        <v>1</v>
-      </c>
-      <c r="F93" s="3">
-        <v>0</v>
-      </c>
-      <c r="G93" s="3">
-        <v>2</v>
-      </c>
-      <c r="H93" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="I93" s="5" t="s">
+      <c r="L93" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="J93" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="103" customHeight="1" spans="3:11">
+    </row>
+    <row r="103" customHeight="1" spans="3:12">
       <c r="C103" s="1">
         <v>201</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E103" s="1">
-        <v>1</v>
-      </c>
-      <c r="F103" s="3">
-        <v>0</v>
+        <v>242</v>
+      </c>
+      <c r="F103" s="1">
+        <v>1</v>
       </c>
       <c r="G103" s="3">
-        <v>2</v>
-      </c>
-      <c r="H103" s="5" t="s">
-        <v>34</v>
+        <v>0</v>
+      </c>
+      <c r="H103" s="3">
+        <v>2</v>
       </c>
       <c r="I103" s="5" t="s">
         <v>35</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K103" s="1" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="104" customHeight="1" spans="3:11">
+        <v>36</v>
+      </c>
+      <c r="K103" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="3:12">
       <c r="C104" s="1">
         <v>202</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E104" s="1">
-        <v>1</v>
-      </c>
-      <c r="F104" s="3">
-        <v>0</v>
+        <v>244</v>
+      </c>
+      <c r="F104" s="1">
+        <v>1</v>
       </c>
       <c r="G104" s="3">
-        <v>2</v>
-      </c>
-      <c r="H104" s="5" t="s">
-        <v>34</v>
+        <v>0</v>
+      </c>
+      <c r="H104" s="3">
+        <v>2</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>244</v>
+        <v>35</v>
       </c>
       <c r="J104" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K104" s="1" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="105" customHeight="1" spans="3:11">
+      <c r="K104" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L104" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="3:12">
       <c r="C105" s="1">
         <v>203</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E105" s="1">
-        <v>1</v>
-      </c>
-      <c r="F105" s="3">
-        <v>0</v>
+        <v>247</v>
+      </c>
+      <c r="F105" s="1">
+        <v>1</v>
       </c>
       <c r="G105" s="3">
-        <v>2</v>
-      </c>
-      <c r="H105" s="5" t="s">
-        <v>34</v>
+        <v>0</v>
+      </c>
+      <c r="H105" s="3">
+        <v>2</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>247</v>
+        <v>35</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K105" s="1" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="106" customHeight="1" spans="3:11">
+      <c r="K105" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L105" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="3:12">
       <c r="C106" s="1">
         <v>204</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="E106" s="1">
-        <v>1</v>
-      </c>
-      <c r="F106" s="3">
-        <v>0</v>
+        <v>250</v>
+      </c>
+      <c r="F106" s="1">
+        <v>1</v>
       </c>
       <c r="G106" s="3">
-        <v>2</v>
-      </c>
-      <c r="H106" s="5" t="s">
-        <v>34</v>
+        <v>0</v>
+      </c>
+      <c r="H106" s="3">
+        <v>2</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>250</v>
+        <v>35</v>
       </c>
       <c r="J106" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K106" s="1" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="107" customHeight="1" spans="3:11">
+      <c r="K106" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L106" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="3:12">
       <c r="C107" s="1">
         <v>205</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E107" s="1">
-        <v>1</v>
-      </c>
-      <c r="F107" s="3">
-        <v>0</v>
+        <v>253</v>
+      </c>
+      <c r="F107" s="1">
+        <v>1</v>
       </c>
       <c r="G107" s="3">
-        <v>2</v>
-      </c>
-      <c r="H107" s="5" t="s">
-        <v>34</v>
+        <v>0</v>
+      </c>
+      <c r="H107" s="3">
+        <v>2</v>
       </c>
       <c r="I107" s="5" t="s">
-        <v>253</v>
+        <v>35</v>
       </c>
       <c r="J107" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K107" s="1" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="108" customHeight="1" spans="3:11">
+      <c r="K107" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L107" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="3:12">
       <c r="C108" s="1">
         <v>206</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E108" s="1">
-        <v>1</v>
-      </c>
-      <c r="F108" s="3">
-        <v>0</v>
+        <v>256</v>
+      </c>
+      <c r="F108" s="1">
+        <v>1</v>
       </c>
       <c r="G108" s="3">
-        <v>2</v>
-      </c>
-      <c r="H108" s="5" t="s">
-        <v>34</v>
+        <v>0</v>
+      </c>
+      <c r="H108" s="3">
+        <v>2</v>
       </c>
       <c r="I108" s="5" t="s">
-        <v>256</v>
+        <v>35</v>
       </c>
       <c r="J108" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K108" s="1" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="109" customHeight="1" spans="3:11">
+      <c r="K108" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L108" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="3:12">
       <c r="C109" s="1">
         <v>207</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="E109" s="1">
-        <v>1</v>
-      </c>
-      <c r="F109" s="3">
-        <v>0</v>
+        <v>259</v>
+      </c>
+      <c r="F109" s="1">
+        <v>1</v>
       </c>
       <c r="G109" s="3">
-        <v>2</v>
-      </c>
-      <c r="H109" s="5" t="s">
-        <v>259</v>
+        <v>0</v>
+      </c>
+      <c r="H109" s="3">
+        <v>2</v>
       </c>
       <c r="I109" s="5" t="s">
         <v>260</v>
@@ -4881,104 +4936,107 @@
       <c r="J109" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="K109" s="1" t="s">
+      <c r="K109" s="5" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="110" customHeight="1" spans="3:11">
+      <c r="L109" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="3:12">
       <c r="C110" s="1">
         <v>208</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="E110" s="1">
-        <v>1</v>
-      </c>
-      <c r="F110" s="3">
-        <v>0</v>
+        <v>264</v>
+      </c>
+      <c r="F110" s="1">
+        <v>1</v>
       </c>
       <c r="G110" s="3">
-        <v>2</v>
-      </c>
-      <c r="H110" s="5" t="s">
-        <v>264</v>
+        <v>0</v>
+      </c>
+      <c r="H110" s="3">
+        <v>2</v>
       </c>
       <c r="I110" s="5" t="s">
         <v>265</v>
       </c>
       <c r="J110" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="K110" s="1" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="111" customHeight="1" spans="3:11">
+      <c r="K110" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="L110" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="3:12">
       <c r="C111" s="1">
         <v>209</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="E111" s="1">
-        <v>1</v>
-      </c>
-      <c r="F111" s="3">
-        <v>0</v>
+        <v>268</v>
+      </c>
+      <c r="F111" s="1">
+        <v>1</v>
       </c>
       <c r="G111" s="3">
-        <v>2</v>
-      </c>
-      <c r="H111" s="5" t="s">
-        <v>259</v>
+        <v>0</v>
+      </c>
+      <c r="H111" s="3">
+        <v>2</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="J111" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="K111" s="1" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="112" customHeight="1" spans="3:11">
+      <c r="K111" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="L111" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="3:12">
       <c r="C112" s="1">
         <v>210</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E112" s="1">
-        <v>1</v>
-      </c>
-      <c r="F112" s="3">
-        <v>0</v>
+        <v>271</v>
+      </c>
+      <c r="F112" s="1">
+        <v>1</v>
       </c>
       <c r="G112" s="3">
-        <v>2</v>
-      </c>
-      <c r="H112" s="5" t="s">
-        <v>271</v>
+        <v>0</v>
+      </c>
+      <c r="H112" s="3">
+        <v>2</v>
       </c>
       <c r="I112" s="5" t="s">
         <v>272</v>
       </c>
       <c r="J112" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="K112" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
+      </c>
+      <c r="K112" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="L112" s="1" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5 H3:K5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 F3:F5 C3:D5 I3:L5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:G5" errorStyle="warning">
-      <formula1>COUNTIF($A:$A,F3)&lt;2</formula1>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G3:H5" errorStyle="warning">
+      <formula1>COUNTIF($A:$A,G3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5013,83 +5071,83 @@
         <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5097,7 +5155,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -5109,16 +5167,16 @@
         <v>2</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5126,7 +5184,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -5138,16 +5196,16 @@
         <v>2</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5155,7 +5213,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -5167,16 +5225,16 @@
         <v>2</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5184,7 +5242,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -5196,16 +5254,16 @@
         <v>2</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5213,7 +5271,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -5225,16 +5283,16 @@
         <v>2</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5242,7 +5300,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -5254,16 +5312,16 @@
         <v>2</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5271,7 +5329,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -5283,16 +5341,16 @@
         <v>2</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5300,7 +5358,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -5312,16 +5370,16 @@
         <v>2</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5329,7 +5387,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -5341,16 +5399,16 @@
         <v>2</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5358,7 +5416,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -5370,16 +5428,16 @@
         <v>2</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I15" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5387,7 +5445,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -5399,16 +5457,16 @@
         <v>2</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I16" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5416,7 +5474,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -5428,16 +5486,16 @@
         <v>2</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I17" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5445,7 +5503,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -5457,16 +5515,16 @@
         <v>2</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I18" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5474,7 +5532,7 @@
         <v>1014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -5486,16 +5544,16 @@
         <v>2</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="18" customHeight="1"/>
@@ -5504,7 +5562,7 @@
         <v>1101</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -5516,16 +5574,16 @@
         <v>2</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5533,7 +5591,7 @@
         <v>1102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -5545,16 +5603,16 @@
         <v>2</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5562,7 +5620,7 @@
         <v>1103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -5574,16 +5632,16 @@
         <v>2</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5591,7 +5649,7 @@
         <v>1104</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -5603,16 +5661,16 @@
         <v>2</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5620,7 +5678,7 @@
         <v>1105</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -5632,16 +5690,16 @@
         <v>2</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5649,7 +5707,7 @@
         <v>1106</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -5661,16 +5719,16 @@
         <v>2</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5678,7 +5736,7 @@
         <v>1107</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -5690,16 +5748,16 @@
         <v>2</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5707,7 +5765,7 @@
         <v>1108</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -5719,16 +5777,16 @@
         <v>2</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5736,7 +5794,7 @@
         <v>1109</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -5748,16 +5806,16 @@
         <v>2</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5765,7 +5823,7 @@
         <v>1110</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -5777,16 +5835,16 @@
         <v>2</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5794,7 +5852,7 @@
         <v>1111</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -5806,16 +5864,16 @@
         <v>2</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="18" customHeight="1" spans="3:11">
@@ -5823,7 +5881,7 @@
         <v>1112</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -5835,16 +5893,16 @@
         <v>2</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="18" customHeight="1" spans="2:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -131,7 +131,7 @@
     <t>1阶技能自选</t>
   </si>
   <si>
-    <t>3,3,3</t>
+    <t>4,4,4</t>
   </si>
   <si>
     <t>1001,2001,3001</t>
@@ -388,12 +388,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1659,7 +1659,6 @@
     </row>
     <row r="34" customHeight="1" spans="1:12">
       <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
       <c r="J34" s="4"/>
     </row>
     <row r="35" customHeight="1" spans="1:12">
@@ -1839,72 +1838,36 @@
     <row r="79" customHeight="1" spans="4:12">
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="1"/>
-      <c r="K79" s="1"/>
       <c r="L79" s="3"/>
     </row>
     <row r="80" customHeight="1" spans="4:12">
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="3"/>
-      <c r="H80" s="3"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1"/>
-      <c r="K80" s="1"/>
       <c r="L80" s="3"/>
     </row>
     <row r="81" customHeight="1" spans="4:12">
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="3"/>
-      <c r="H81" s="3"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
-      <c r="K81" s="1"/>
       <c r="L81" s="3"/>
     </row>
     <row r="82" customHeight="1" spans="4:12">
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="3"/>
-      <c r="H82" s="3"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-      <c r="K82" s="1"/>
       <c r="L82" s="3"/>
     </row>
     <row r="83" customHeight="1" spans="4:12">
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
-      <c r="F83" s="1"/>
-      <c r="G83" s="3"/>
-      <c r="H83" s="3"/>
-      <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
-      <c r="K83" s="1"/>
       <c r="L83" s="3"/>
     </row>
     <row r="84" customHeight="1" spans="4:12">
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
-      <c r="F84" s="1"/>
-      <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-      <c r="I84" s="1"/>
-      <c r="J84" s="1"/>
-      <c r="K84" s="1"/>
       <c r="L84" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 F3:F5 C3:D5 I3:L5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5 I3:L5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G3:H5" errorStyle="warning">
@@ -2315,7 +2278,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,E3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="53">
   <si>
     <t>_id</t>
   </si>
@@ -195,6 +195,39 @@
   </si>
   <si>
     <t>1,2,3</t>
+  </si>
+  <si>
+    <t>战士技能全选</t>
+  </si>
+  <si>
+    <t>4,4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>1001,1002,1003,1004,1005,1006,1007</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1</t>
+  </si>
+  <si>
+    <t>战士1-7阶技能各1本</t>
+  </si>
+  <si>
+    <t>法师技能全选</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,2004,2005,2006,2007</t>
+  </si>
+  <si>
+    <t>法师1-7阶技能各1本</t>
+  </si>
+  <si>
+    <t>道士技能全选</t>
+  </si>
+  <si>
+    <t>3001,3002,3003,3004,3005,3006,3007</t>
+  </si>
+  <si>
+    <t>道士1-7阶技能各1本</t>
   </si>
   <si>
     <t>金色刺杀自选</t>
@@ -388,12 +421,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1305,7 +1338,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="1">
         <v>2</v>
@@ -1337,7 +1370,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="1">
         <v>2</v>
@@ -1369,7 +1402,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="1">
         <v>2</v>
@@ -1401,7 +1434,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="1">
         <v>2</v>
@@ -1433,7 +1466,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="1">
         <v>2</v>
@@ -1465,7 +1498,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1">
         <v>2</v>
@@ -1497,7 +1530,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="1">
         <v>2</v>
@@ -1529,7 +1562,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="1">
         <v>2</v>
@@ -1561,7 +1594,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="1">
         <v>2</v>
@@ -1592,8 +1625,8 @@
       <c r="F15" s="1">
         <v>1</v>
       </c>
-      <c r="G15" s="3">
-        <v>0</v>
+      <c r="G15" s="1">
+        <v>1</v>
       </c>
       <c r="H15" s="3">
         <v>2</v>
@@ -1611,47 +1644,134 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="7:8">
+    <row r="17" customHeight="1" spans="3:12">
       <c r="H17" s="1"/>
     </row>
-    <row r="18" customHeight="1" spans="7:8">
+    <row r="18" customHeight="1" spans="3:12">
       <c r="H18" s="1"/>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1"/>
-    <row r="20" customHeight="1" spans="7:8">
+    <row r="20" customHeight="1" spans="3:12">
       <c r="H20" s="1"/>
     </row>
-    <row r="21" customHeight="1" spans="7:8">
-      <c r="H21" s="1"/>
-    </row>
-    <row r="22" customHeight="1" spans="7:8">
-      <c r="H22" s="1"/>
-    </row>
-    <row r="23" customHeight="1" spans="7:8">
-      <c r="H23" s="1"/>
-    </row>
-    <row r="24" customHeight="1" spans="7:8">
+    <row r="21" customHeight="1" spans="3:12">
+      <c r="C21" s="1">
+        <v>11</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="1">
+        <v>5</v>
+      </c>
+      <c r="F21" s="1">
+        <v>2</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1">
+        <v>2</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:12">
+      <c r="C22" s="1">
+        <v>12</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" s="1">
+        <v>5</v>
+      </c>
+      <c r="F22" s="1">
+        <v>2</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1">
+        <v>2</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:12">
+      <c r="C23" s="1">
+        <v>13</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="1">
+        <v>5</v>
+      </c>
+      <c r="F23" s="1">
+        <v>2</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1</v>
+      </c>
+      <c r="H23" s="1">
+        <v>2</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:12">
       <c r="H24" s="1"/>
     </row>
-    <row r="25" customHeight="1" spans="7:8">
+    <row r="25" customHeight="1" spans="3:12">
       <c r="H25" s="1"/>
     </row>
-    <row r="26" customHeight="1" spans="7:8">
+    <row r="26" customHeight="1" spans="3:12">
       <c r="H26" s="1"/>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1"/>
     <row r="28" s="1" customFormat="1" customHeight="1"/>
-    <row r="29" customHeight="1" spans="7:8">
+    <row r="29" customHeight="1" spans="3:12">
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" customHeight="1" spans="7:8">
+    <row r="30" customHeight="1" spans="3:12">
       <c r="H30" s="1"/>
     </row>
-    <row r="31" customHeight="1" spans="7:8">
+    <row r="31" customHeight="1" spans="3:12">
       <c r="H31" s="1"/>
     </row>
-    <row r="32" customHeight="1" spans="7:8">
+    <row r="32" customHeight="1" spans="3:12">
       <c r="H32" s="1"/>
     </row>
     <row r="33" customHeight="1" spans="1:12">
@@ -2005,7 +2125,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E6" s="1">
         <v>7</v>
@@ -2020,16 +2140,16 @@
         <v>2</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="61">
   <si>
     <t>_id</t>
   </si>
@@ -195,6 +195,30 @@
   </si>
   <si>
     <t>1,2,3</t>
+  </si>
+  <si>
+    <t>四格碎片包</t>
+  </si>
+  <si>
+    <t>5,5,5,5</t>
+  </si>
+  <si>
+    <t>5011,5012,5013,5014</t>
+  </si>
+  <si>
+    <t>1,1,1,1</t>
+  </si>
+  <si>
+    <t>区域1-4珍品材料自选</t>
+  </si>
+  <si>
+    <t>5,5,5,5,5,5,5,5,5,5,5,5</t>
+  </si>
+  <si>
+    <t>40000001,40000002,40000003,40000004,40000005,40000006,40000007,40000008,40000009,40000010,40000011,40000012</t>
+  </si>
+  <si>
+    <t>25,3,1,25,3,1,25,3,1,25,3,1</t>
   </si>
   <si>
     <t>战士技能全选</t>
@@ -1644,8 +1668,69 @@
         <v>34</v>
       </c>
     </row>
+    <row r="16" customHeight="1" spans="3:12">
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="1">
+        <v>5</v>
+      </c>
+      <c r="F16" s="1">
+        <v>2</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
     <row r="17" customHeight="1" spans="3:12">
-      <c r="H17" s="1"/>
+      <c r="C17" s="1">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="1">
+        <v>5</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1">
+        <v>2</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="18" customHeight="1" spans="3:12">
       <c r="H18" s="1"/>
@@ -1656,10 +1741,10 @@
     </row>
     <row r="21" customHeight="1" spans="3:12">
       <c r="C21" s="1">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E21" s="1">
         <v>5</v>
@@ -1674,24 +1759,24 @@
         <v>2</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:12">
       <c r="C22" s="1">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E22" s="1">
         <v>5</v>
@@ -1706,24 +1791,24 @@
         <v>2</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:12">
       <c r="C23" s="1">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E23" s="1">
         <v>5</v>
@@ -1738,16 +1823,16 @@
         <v>2</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:12">
@@ -2125,7 +2210,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E6" s="1">
         <v>7</v>
@@ -2140,16 +2225,16 @@
         <v>2</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="62">
   <si>
     <t>_id</t>
   </si>
@@ -207,6 +207,9 @@
   </si>
   <si>
     <t>1,1,1,1</t>
+  </si>
+  <si>
+    <t>每种四格碎片材料各一个</t>
   </si>
   <si>
     <t>区域1-4珍品材料自选</t>
@@ -1697,7 +1700,7 @@
         <v>40</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:12">
@@ -1705,7 +1708,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E17" s="1">
         <v>5</v>
@@ -1720,16 +1723,16 @@
         <v>2</v>
       </c>
       <c r="I17" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:12">
@@ -1744,7 +1747,7 @@
         <v>101</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E21" s="1">
         <v>5</v>
@@ -1759,16 +1762,16 @@
         <v>2</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:12">
@@ -1776,7 +1779,7 @@
         <v>102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E22" s="1">
         <v>5</v>
@@ -1791,16 +1794,16 @@
         <v>2</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:12">
@@ -1808,7 +1811,7 @@
         <v>103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E23" s="1">
         <v>5</v>
@@ -1823,16 +1826,16 @@
         <v>2</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:12">
@@ -2210,7 +2213,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E6" s="1">
         <v>7</v>
@@ -2225,16 +2228,16 @@
         <v>2</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="65">
   <si>
     <t>_id</t>
   </si>
@@ -113,12 +113,18 @@
     <t>ItemCountList</t>
   </si>
   <si>
+    <t>堆叠数量</t>
+  </si>
+  <si>
     <t>Des</t>
   </si>
   <si>
     <t>Id</t>
   </si>
   <si>
+    <t>MaxNum</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -126,6 +132,9 @@
   </si>
   <si>
     <t>int[]</t>
+  </si>
+  <si>
+    <t>long</t>
   </si>
   <si>
     <t>1阶技能自选</t>
@@ -1241,7 +1250,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:L84"/>
+  <dimension ref="A3:M84"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1249,13 +1258,13 @@
     <col min="6" max="6" width="14.1666666666667" style="1" customWidth="1"/>
     <col min="7" max="8" width="13.0833333333333" style="3" customWidth="1"/>
     <col min="9" max="9" width="31.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="72.0166666666667" style="1" customWidth="1"/>
-    <col min="11" max="11" width="26.875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="42.25" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="10" max="10" width="58.8333333333333" style="1" customWidth="1"/>
+    <col min="11" max="12" width="26.875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="42.25" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" customHeight="1" spans="3:12">
+    <row r="3" customHeight="1" spans="3:13">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1286,10 +1295,13 @@
       <c r="L3" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" customHeight="1" spans="3:12">
+      <c r="M3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="3:13">
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>1</v>
@@ -1316,47 +1328,53 @@
         <v>8</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="3:12">
+        <v>12</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="3:13">
       <c r="C5" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>16</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E6" s="1">
         <v>3</v>
@@ -1371,24 +1389,27 @@
         <v>2</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -1403,24 +1424,27 @@
         <v>2</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>20</v>
+      </c>
+      <c r="L7" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -1435,24 +1459,27 @@
         <v>2</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L8" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="L8" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -1467,24 +1494,27 @@
         <v>2</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>20</v>
+      </c>
+      <c r="L9" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
@@ -1499,24 +1529,27 @@
         <v>2</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>20</v>
+      </c>
+      <c r="L10" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
@@ -1531,24 +1564,27 @@
         <v>2</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>20</v>
+      </c>
+      <c r="L11" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
@@ -1563,24 +1599,27 @@
         <v>2</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:12">
+        <v>20</v>
+      </c>
+      <c r="L12" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:13">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E13" s="1">
         <v>5</v>
@@ -1595,24 +1634,27 @@
         <v>2</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:12">
+        <v>20</v>
+      </c>
+      <c r="L13" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:13">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E14" s="1">
         <v>5</v>
@@ -1627,24 +1669,27 @@
         <v>2</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:12">
+        <v>20</v>
+      </c>
+      <c r="L14" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:13">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E15" s="1">
         <v>3</v>
@@ -1659,24 +1704,27 @@
         <v>2</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:12">
+        <v>20</v>
+      </c>
+      <c r="L15" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:13">
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E16" s="1">
         <v>5</v>
@@ -1691,24 +1739,27 @@
         <v>1</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:12">
+        <v>43</v>
+      </c>
+      <c r="L16" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:13">
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E17" s="1">
         <v>5</v>
@@ -1723,31 +1774,34 @@
         <v>2</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L17" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:12">
+    </row>
+    <row r="18" customHeight="1" spans="3:13">
       <c r="H18" s="1"/>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1"/>
-    <row r="20" customHeight="1" spans="3:12">
+    <row r="20" customHeight="1" spans="3:13">
       <c r="H20" s="1"/>
     </row>
-    <row r="21" customHeight="1" spans="3:12">
+    <row r="21" customHeight="1" spans="3:13">
       <c r="C21" s="1">
         <v>101</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E21" s="1">
         <v>5</v>
@@ -1762,24 +1816,27 @@
         <v>2</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:12">
+        <v>52</v>
+      </c>
+      <c r="L21" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:13">
       <c r="C22" s="1">
         <v>102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E22" s="1">
         <v>5</v>
@@ -1794,24 +1851,27 @@
         <v>2</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J22" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="K22" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="K22" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:12">
+      <c r="L22" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:13">
       <c r="C23" s="1">
         <v>103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E23" s="1">
         <v>5</v>
@@ -1826,65 +1886,68 @@
         <v>2</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:12">
+        <v>52</v>
+      </c>
+      <c r="L23" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:13">
       <c r="H24" s="1"/>
     </row>
-    <row r="25" customHeight="1" spans="3:12">
+    <row r="25" customHeight="1" spans="3:13">
       <c r="H25" s="1"/>
     </row>
-    <row r="26" customHeight="1" spans="3:12">
+    <row r="26" customHeight="1" spans="3:13">
       <c r="H26" s="1"/>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1"/>
     <row r="28" s="1" customFormat="1" customHeight="1"/>
-    <row r="29" customHeight="1" spans="3:12">
+    <row r="29" customHeight="1" spans="3:13">
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" customHeight="1" spans="3:12">
+    <row r="30" customHeight="1" spans="3:13">
       <c r="H30" s="1"/>
     </row>
-    <row r="31" customHeight="1" spans="3:12">
+    <row r="31" customHeight="1" spans="3:13">
       <c r="H31" s="1"/>
     </row>
-    <row r="32" customHeight="1" spans="3:12">
+    <row r="32" customHeight="1" spans="3:13">
       <c r="H32" s="1"/>
     </row>
-    <row r="33" customHeight="1" spans="1:12">
+    <row r="33" customHeight="1" spans="1:13">
       <c r="H33" s="1"/>
     </row>
-    <row r="34" customHeight="1" spans="1:12">
+    <row r="34" customHeight="1" spans="1:13">
       <c r="H34" s="1"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" customHeight="1" spans="1:12">
+    <row r="35" customHeight="1" spans="1:13">
       <c r="H35" s="1"/>
     </row>
-    <row r="36" customHeight="1" spans="1:12">
+    <row r="36" customHeight="1" spans="1:13">
       <c r="H36" s="1"/>
     </row>
-    <row r="37" customHeight="1" spans="1:12">
+    <row r="37" customHeight="1" spans="1:13">
       <c r="H37" s="1"/>
     </row>
-    <row r="38" customHeight="1" spans="1:12">
+    <row r="38" customHeight="1" spans="1:13">
       <c r="H38" s="1"/>
     </row>
-    <row r="39" customHeight="1" spans="1:12">
+    <row r="39" customHeight="1" spans="1:13">
       <c r="H39" s="1"/>
     </row>
-    <row r="40" customFormat="1" customHeight="1" spans="1:12">
+    <row r="40" customFormat="1" customHeight="1" spans="1:13">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -1897,29 +1960,30 @@
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:12">
+      <c r="M40" s="1"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:13">
       <c r="H41" s="1"/>
     </row>
-    <row r="43" customHeight="1" spans="1:12">
+    <row r="43" customHeight="1" spans="1:13">
       <c r="H43" s="1"/>
     </row>
-    <row r="44" customHeight="1" spans="1:12">
+    <row r="44" customHeight="1" spans="1:13">
       <c r="H44" s="1"/>
     </row>
-    <row r="45" customHeight="1" spans="1:12">
+    <row r="45" customHeight="1" spans="1:13">
       <c r="H45" s="1"/>
     </row>
-    <row r="46" customHeight="1" spans="1:12">
+    <row r="46" customHeight="1" spans="1:13">
       <c r="H46" s="1"/>
     </row>
-    <row r="47" customHeight="1" spans="1:12">
+    <row r="47" customHeight="1" spans="1:13">
       <c r="H47" s="1"/>
     </row>
-    <row r="48" customHeight="1" spans="1:12">
+    <row r="48" customHeight="1" spans="1:13">
       <c r="H48" s="1"/>
     </row>
-    <row r="49" customFormat="1" customHeight="1" spans="1:12">
+    <row r="49" customFormat="1" customHeight="1" spans="1:13">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -1932,9 +1996,10 @@
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1"/>
-    <row r="51" customFormat="1" customHeight="1" spans="1:12">
+    <row r="51" customFormat="1" customHeight="1" spans="1:13">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -1947,8 +2012,9 @@
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
-    </row>
-    <row r="52" customFormat="1" customHeight="1" spans="1:12">
+      <c r="M51" s="1"/>
+    </row>
+    <row r="52" customFormat="1" customHeight="1" spans="1:13">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -1961,8 +2027,9 @@
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
-    </row>
-    <row r="53" customFormat="1" customHeight="1" spans="1:12">
+      <c r="M52" s="1"/>
+    </row>
+    <row r="53" customFormat="1" customHeight="1" spans="1:13">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -1975,8 +2042,9 @@
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
-    </row>
-    <row r="54" customFormat="1" customHeight="1" spans="1:12">
+      <c r="M53" s="1"/>
+    </row>
+    <row r="54" customFormat="1" customHeight="1" spans="1:13">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -1989,8 +2057,9 @@
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
-    </row>
-    <row r="55" customFormat="1" customHeight="1" spans="1:12">
+      <c r="M54" s="1"/>
+    </row>
+    <row r="55" customFormat="1" customHeight="1" spans="1:13">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2003,79 +2072,80 @@
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
-    </row>
-    <row r="56" customHeight="1" spans="1:12">
+      <c r="M55" s="1"/>
+    </row>
+    <row r="56" customHeight="1" spans="1:13">
       <c r="H56" s="1"/>
     </row>
-    <row r="57" customHeight="1" spans="1:12">
+    <row r="57" customHeight="1" spans="1:13">
       <c r="H57" s="1"/>
     </row>
-    <row r="58" customHeight="1" spans="1:12">
+    <row r="58" customHeight="1" spans="1:13">
       <c r="H58" s="1"/>
     </row>
-    <row r="59" customHeight="1" spans="1:12">
+    <row r="59" customHeight="1" spans="1:13">
       <c r="H59" s="1"/>
     </row>
-    <row r="60" customHeight="1" spans="1:12">
+    <row r="60" customHeight="1" spans="1:13">
       <c r="H60" s="1"/>
     </row>
-    <row r="61" customHeight="1" spans="1:12">
+    <row r="61" customHeight="1" spans="1:13">
       <c r="H61" s="1"/>
     </row>
-    <row r="62" customHeight="1" spans="1:12">
+    <row r="62" customHeight="1" spans="1:13">
       <c r="H62" s="1"/>
     </row>
-    <row r="63" customHeight="1" spans="1:12">
+    <row r="63" customHeight="1" spans="1:13">
       <c r="H63" s="1"/>
     </row>
-    <row r="64" customHeight="1" spans="1:12">
+    <row r="64" customHeight="1" spans="1:13">
       <c r="H64" s="1"/>
     </row>
-    <row r="65" customHeight="1" spans="4:12">
+    <row r="65" customHeight="1" spans="4:13">
       <c r="H65" s="1"/>
     </row>
-    <row r="67" customHeight="1" spans="4:12">
+    <row r="67" customHeight="1" spans="4:13">
       <c r="H67" s="1"/>
     </row>
-    <row r="68" customHeight="1" spans="4:12">
+    <row r="68" customHeight="1" spans="4:13">
       <c r="H68" s="1"/>
     </row>
-    <row r="69" customHeight="1" spans="4:12">
+    <row r="69" customHeight="1" spans="4:13">
       <c r="H69" s="1"/>
     </row>
-    <row r="79" customHeight="1" spans="4:12">
+    <row r="79" customHeight="1" spans="4:13">
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
-      <c r="L79" s="3"/>
-    </row>
-    <row r="80" customHeight="1" spans="4:12">
+      <c r="M79" s="3"/>
+    </row>
+    <row r="80" customHeight="1" spans="4:13">
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
-      <c r="L80" s="3"/>
-    </row>
-    <row r="81" customHeight="1" spans="4:12">
+      <c r="M80" s="3"/>
+    </row>
+    <row r="81" customHeight="1" spans="4:13">
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" customHeight="1" spans="4:12">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" customHeight="1" spans="4:13">
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
-      <c r="L82" s="3"/>
-    </row>
-    <row r="83" customHeight="1" spans="4:12">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" customHeight="1" spans="4:13">
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" customHeight="1" spans="4:12">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" customHeight="1" spans="4:13">
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
-      <c r="L84" s="3"/>
+      <c r="M84" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5 I3:L5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:M5 I3:K5 C3:F5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G3:H5" errorStyle="warning">
@@ -2141,12 +2211,12 @@
         <v>8</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="18" customHeight="1" spans="3:12">
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>1</v>
@@ -2173,39 +2243,39 @@
         <v>8</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="3:12">
       <c r="C5" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="3:12">
@@ -2213,7 +2283,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E6" s="1">
         <v>7</v>
@@ -2228,16 +2298,16 @@
         <v>2</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="68">
   <si>
     <t>_id</t>
   </si>
@@ -231,6 +231,15 @@
   </si>
   <si>
     <t>25,3,1,25,3,1,25,3,1,25,3,1</t>
+  </si>
+  <si>
+    <t>区域5-8珍品材料自选</t>
+  </si>
+  <si>
+    <t>5,5,5,5,5,5</t>
+  </si>
+  <si>
+    <t>40000013,40000014,40000015,40000016,40000017,40000018</t>
   </si>
   <si>
     <t>战士技能全选</t>
@@ -1790,7 +1799,39 @@
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:13">
-      <c r="H18" s="1"/>
+      <c r="C18" s="1">
+        <v>13</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="1">
+        <v>5</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1">
+        <v>2</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L18" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1"/>
     <row r="20" customHeight="1" spans="3:13">
@@ -1801,7 +1842,7 @@
         <v>101</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E21" s="1">
         <v>5</v>
@@ -1816,19 +1857,19 @@
         <v>2</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L21" s="1">
         <v>9999</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:13">
@@ -1836,7 +1877,7 @@
         <v>102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E22" s="1">
         <v>5</v>
@@ -1851,19 +1892,19 @@
         <v>2</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J22" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K22" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="L22" s="1">
         <v>9999</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:13">
@@ -1871,7 +1912,7 @@
         <v>103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E23" s="1">
         <v>5</v>
@@ -1886,19 +1927,19 @@
         <v>2</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L23" s="1">
         <v>9999</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:13">
@@ -2145,7 +2186,7 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:M5 I3:K5 C3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:M5 C3:F5 I3:K5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G3:H5" errorStyle="warning">
@@ -2283,7 +2324,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E6" s="1">
         <v>7</v>
@@ -2298,16 +2339,16 @@
         <v>2</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -84,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="70">
   <si>
     <t>_id</t>
   </si>
@@ -240,6 +245,12 @@
   </si>
   <si>
     <t>40000013,40000014,40000015,40000016,40000017,40000018</t>
+  </si>
+  <si>
+    <t>多重宠物礼包</t>
+  </si>
+  <si>
+    <t>4,5,6</t>
   </si>
   <si>
     <t>战士技能全选</t>
@@ -1833,7 +1844,41 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1"/>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C19" s="1">
+        <v>14</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="1">
+        <v>3</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+      <c r="H19" s="3">
+        <v>2</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L19" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
     <row r="20" customHeight="1" spans="3:13">
       <c r="H20" s="1"/>
     </row>
@@ -1842,7 +1887,7 @@
         <v>101</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E21" s="1">
         <v>5</v>
@@ -1857,19 +1902,19 @@
         <v>2</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L21" s="1">
         <v>9999</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:13">
@@ -1877,7 +1922,7 @@
         <v>102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E22" s="1">
         <v>5</v>
@@ -1892,19 +1937,19 @@
         <v>2</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L22" s="1">
         <v>9999</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:13">
@@ -1912,7 +1957,7 @@
         <v>103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E23" s="1">
         <v>5</v>
@@ -1927,19 +1972,19 @@
         <v>2</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L23" s="1">
         <v>9999</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:13">
@@ -2324,7 +2369,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E6" s="1">
         <v>7</v>
@@ -2339,16 +2384,16 @@
         <v>2</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="72">
   <si>
     <t>_id</t>
   </si>
@@ -251,6 +251,12 @@
   </si>
   <si>
     <t>4,5,6</t>
+  </si>
+  <si>
+    <t>双减宠物礼包</t>
+  </si>
+  <si>
+    <t>7,8,9</t>
   </si>
   <si>
     <t>战士技能全选</t>
@@ -1270,7 +1276,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:M84"/>
+  <dimension ref="A3:M85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1879,50 +1885,50 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="3:13">
-      <c r="H20" s="1"/>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C20" s="1">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="1">
+        <v>3</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+      <c r="H20" s="3">
+        <v>2</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L20" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="21" customHeight="1" spans="3:13">
-      <c r="C21" s="1">
-        <v>101</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" s="1">
-        <v>5</v>
-      </c>
-      <c r="F21" s="1">
-        <v>2</v>
-      </c>
-      <c r="G21" s="1">
-        <v>1</v>
-      </c>
-      <c r="H21" s="1">
-        <v>2</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="L21" s="1">
-        <v>9999</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>58</v>
-      </c>
+      <c r="H21" s="1"/>
     </row>
     <row r="22" customHeight="1" spans="3:13">
       <c r="C22" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E22" s="1">
         <v>5</v>
@@ -1937,27 +1943,27 @@
         <v>2</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L22" s="1">
         <v>9999</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:13">
       <c r="C23" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E23" s="1">
         <v>5</v>
@@ -1972,23 +1978,55 @@
         <v>2</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L23" s="1">
         <v>9999</v>
       </c>
       <c r="M23" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:13">
+      <c r="C24" s="1">
+        <v>103</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:13">
-      <c r="H24" s="1"/>
+      <c r="E24" s="1">
+        <v>5</v>
+      </c>
+      <c r="F24" s="1">
+        <v>2</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1">
+        <v>2</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="L24" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="25" customHeight="1" spans="3:13">
       <c r="H25" s="1"/>
@@ -1996,13 +2034,13 @@
     <row r="26" customHeight="1" spans="3:13">
       <c r="H26" s="1"/>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1"/>
+    <row r="27" customHeight="1" spans="3:13">
+      <c r="H27" s="1"/>
+    </row>
     <row r="28" s="1" customFormat="1" customHeight="1"/>
-    <row r="29" customHeight="1" spans="3:13">
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1"/>
     <row r="30" customHeight="1" spans="3:13">
+      <c r="G30" s="1"/>
       <c r="H30" s="1"/>
     </row>
     <row r="31" customHeight="1" spans="3:13">
@@ -2016,10 +2054,10 @@
     </row>
     <row r="34" customHeight="1" spans="1:13">
       <c r="H34" s="1"/>
-      <c r="J34" s="4"/>
     </row>
     <row r="35" customHeight="1" spans="1:13">
       <c r="H35" s="1"/>
+      <c r="J35" s="4"/>
     </row>
     <row r="36" customHeight="1" spans="1:13">
       <c r="H36" s="1"/>
@@ -2033,26 +2071,26 @@
     <row r="39" customHeight="1" spans="1:13">
       <c r="H39" s="1"/>
     </row>
-    <row r="40" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="3"/>
-      <c r="H40"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:13">
-      <c r="H41" s="1"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:13">
-      <c r="H43" s="1"/>
+    <row r="40" customHeight="1" spans="1:13">
+      <c r="H40" s="1"/>
+    </row>
+    <row r="41" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="3"/>
+      <c r="H41"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:13">
+      <c r="H42" s="1"/>
     </row>
     <row r="44" customHeight="1" spans="1:13">
       <c r="H44" s="1"/>
@@ -2069,37 +2107,25 @@
     <row r="48" customHeight="1" spans="1:13">
       <c r="H48" s="1"/>
     </row>
-    <row r="49" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
-    </row>
-    <row r="50" s="1" customFormat="1" customHeight="1"/>
-    <row r="51" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-      <c r="M51" s="1"/>
-    </row>
+    <row r="49" customHeight="1" spans="1:13">
+      <c r="H49" s="1"/>
+    </row>
+    <row r="50" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+    </row>
+    <row r="51" s="1" customFormat="1" customHeight="1"/>
     <row r="52" customFormat="1" customHeight="1" spans="1:13">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
@@ -2108,7 +2134,7 @@
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="3"/>
-      <c r="H52" s="1"/>
+      <c r="H52" s="3"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -2160,8 +2186,20 @@
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
     </row>
-    <row r="56" customHeight="1" spans="1:13">
+    <row r="56" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="3"/>
       <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
     </row>
     <row r="57" customHeight="1" spans="1:13">
       <c r="H57" s="1"/>
@@ -2190,8 +2228,8 @@
     <row r="65" customHeight="1" spans="4:13">
       <c r="H65" s="1"/>
     </row>
-    <row r="67" customHeight="1" spans="4:13">
-      <c r="H67" s="1"/>
+    <row r="66" customHeight="1" spans="4:13">
+      <c r="H66" s="1"/>
     </row>
     <row r="68" customHeight="1" spans="4:13">
       <c r="H68" s="1"/>
@@ -2199,10 +2237,8 @@
     <row r="69" customHeight="1" spans="4:13">
       <c r="H69" s="1"/>
     </row>
-    <row r="79" customHeight="1" spans="4:13">
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-      <c r="M79" s="3"/>
+    <row r="70" customHeight="1" spans="4:13">
+      <c r="H70" s="1"/>
     </row>
     <row r="80" customHeight="1" spans="4:13">
       <c r="D80" s="3"/>
@@ -2228,6 +2264,11 @@
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="M84" s="3"/>
+    </row>
+    <row r="85" customHeight="1" spans="4:13">
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="M85" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -2369,7 +2410,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E6" s="1">
         <v>7</v>
@@ -2384,16 +2425,16 @@
         <v>2</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:12">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="73">
   <si>
     <t>_id</t>
   </si>
@@ -226,27 +226,33 @@
     <t>每种四格碎片材料各一个</t>
   </si>
   <si>
+    <t>区域1-6珍品材料自选</t>
+  </si>
+  <si>
+    <t>5,5,5,5,5,5,5,5,5,5,5,5</t>
+  </si>
+  <si>
+    <t>40000003,40000006,40000009,40000012,40000015,40000018</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1</t>
+  </si>
+  <si>
     <t>区域1-4珍品材料自选</t>
   </si>
   <si>
-    <t>5,5,5,5,5,5,5,5,5,5,5,5</t>
-  </si>
-  <si>
-    <t>40000001,40000002,40000003,40000004,40000005,40000006,40000007,40000008,40000009,40000010,40000011,40000012</t>
-  </si>
-  <si>
-    <t>25,3,1,25,3,1,25,3,1,25,3,1</t>
+    <t>区域7-12珍品材料自选</t>
+  </si>
+  <si>
+    <t>5,5,5,5,5,5</t>
+  </si>
+  <si>
+    <t>40000021,40000024,40000027,40000030,40000033,40000036</t>
   </si>
   <si>
     <t>区域5-8珍品材料自选</t>
   </si>
   <si>
-    <t>5,5,5,5,5,5</t>
-  </si>
-  <si>
-    <t>40000013,40000014,40000015,40000016,40000017,40000018</t>
-  </si>
-  <si>
     <t>多重宠物礼包</t>
   </si>
   <si>
@@ -266,9 +272,6 @@
   </si>
   <si>
     <t>1001,1002,1003,1004,1005,1006,1007</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,1</t>
   </si>
   <si>
     <t>战士1-7阶技能各1本</t>
@@ -1276,7 +1279,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:M85"/>
+  <dimension ref="A3:M86"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1797,7 +1800,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>46</v>
@@ -1812,7 +1815,7 @@
         <v>9999</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:13">
@@ -1820,7 +1823,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E18" s="1">
         <v>5</v>
@@ -1832,13 +1835,13 @@
         <v>1</v>
       </c>
       <c r="H18" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>48</v>
@@ -1847,7 +1850,7 @@
         <v>9999</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1855,7 +1858,7 @@
         <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -1873,7 +1876,7 @@
         <v>38</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K19" s="5" t="s">
         <v>20</v>
@@ -1882,7 +1885,7 @@
         <v>9999</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1890,7 +1893,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
@@ -1908,7 +1911,7 @@
         <v>38</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>20</v>
@@ -1917,53 +1920,21 @@
         <v>9999</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:13">
       <c r="H21" s="1"/>
     </row>
     <row r="22" customHeight="1" spans="3:13">
-      <c r="C22" s="1">
-        <v>101</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E22" s="1">
-        <v>5</v>
-      </c>
-      <c r="F22" s="1">
-        <v>2</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1</v>
-      </c>
-      <c r="H22" s="1">
-        <v>2</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="L22" s="1">
-        <v>9999</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>60</v>
-      </c>
+      <c r="H22" s="1"/>
     </row>
     <row r="23" customHeight="1" spans="3:13">
       <c r="C23" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E23" s="1">
         <v>5</v>
@@ -1978,27 +1949,27 @@
         <v>2</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="L23" s="1">
         <v>9999</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:13">
       <c r="C24" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E24" s="1">
         <v>5</v>
@@ -2013,23 +1984,55 @@
         <v>2</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="L24" s="1">
         <v>9999</v>
       </c>
       <c r="M24" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:13">
+      <c r="C25" s="1">
+        <v>103</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="1">
+        <v>5</v>
+      </c>
+      <c r="F25" s="1">
+        <v>2</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1">
+        <v>2</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J25" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:13">
-      <c r="H25" s="1"/>
+      <c r="K25" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L25" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="26" customHeight="1" spans="3:13">
       <c r="H26" s="1"/>
@@ -2037,13 +2040,13 @@
     <row r="27" customHeight="1" spans="3:13">
       <c r="H27" s="1"/>
     </row>
-    <row r="28" s="1" customFormat="1" customHeight="1"/>
+    <row r="28" customHeight="1" spans="3:13">
+      <c r="H28" s="1"/>
+    </row>
     <row r="29" s="1" customFormat="1" customHeight="1"/>
-    <row r="30" customHeight="1" spans="3:13">
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1"/>
     <row r="31" customHeight="1" spans="3:13">
+      <c r="G31" s="1"/>
       <c r="H31" s="1"/>
     </row>
     <row r="32" customHeight="1" spans="3:13">
@@ -2057,10 +2060,10 @@
     </row>
     <row r="35" customHeight="1" spans="1:13">
       <c r="H35" s="1"/>
-      <c r="J35" s="4"/>
     </row>
     <row r="36" customHeight="1" spans="1:13">
       <c r="H36" s="1"/>
+      <c r="J36" s="4"/>
     </row>
     <row r="37" customHeight="1" spans="1:13">
       <c r="H37" s="1"/>
@@ -2074,26 +2077,26 @@
     <row r="40" customHeight="1" spans="1:13">
       <c r="H40" s="1"/>
     </row>
-    <row r="41" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="3"/>
-      <c r="H41"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:13">
-      <c r="H42" s="1"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:13">
-      <c r="H44" s="1"/>
+    <row r="41" customHeight="1" spans="1:13">
+      <c r="H41" s="1"/>
+    </row>
+    <row r="42" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="3"/>
+      <c r="H42"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:13">
+      <c r="H43" s="1"/>
     </row>
     <row r="45" customHeight="1" spans="1:13">
       <c r="H45" s="1"/>
@@ -2110,37 +2113,25 @@
     <row r="49" customHeight="1" spans="1:13">
       <c r="H49" s="1"/>
     </row>
-    <row r="50" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
-    </row>
-    <row r="51" s="1" customFormat="1" customHeight="1"/>
-    <row r="52" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
-    </row>
+    <row r="50" customHeight="1" spans="1:13">
+      <c r="H50" s="1"/>
+    </row>
+    <row r="51" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+    </row>
+    <row r="52" s="1" customFormat="1" customHeight="1"/>
     <row r="53" customFormat="1" customHeight="1" spans="1:13">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
@@ -2149,7 +2140,7 @@
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="3"/>
-      <c r="H53" s="1"/>
+      <c r="H53" s="3"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
@@ -2201,8 +2192,20 @@
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
     </row>
-    <row r="57" customHeight="1" spans="1:13">
+    <row r="57" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="3"/>
       <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
     </row>
     <row r="58" customHeight="1" spans="1:13">
       <c r="H58" s="1"/>
@@ -2225,25 +2228,23 @@
     <row r="64" customHeight="1" spans="1:13">
       <c r="H64" s="1"/>
     </row>
-    <row r="65" customHeight="1" spans="4:13">
+    <row r="65" customHeight="1" spans="8:8">
       <c r="H65" s="1"/>
     </row>
-    <row r="66" customHeight="1" spans="4:13">
+    <row r="66" customHeight="1" spans="8:8">
       <c r="H66" s="1"/>
     </row>
-    <row r="68" customHeight="1" spans="4:13">
-      <c r="H68" s="1"/>
-    </row>
-    <row r="69" customHeight="1" spans="4:13">
+    <row r="67" customHeight="1" spans="8:8">
+      <c r="H67" s="1"/>
+    </row>
+    <row r="69" customHeight="1" spans="8:8">
       <c r="H69" s="1"/>
     </row>
-    <row r="70" customHeight="1" spans="4:13">
+    <row r="70" customHeight="1" spans="8:8">
       <c r="H70" s="1"/>
     </row>
-    <row r="80" customHeight="1" spans="4:13">
-      <c r="D80" s="3"/>
-      <c r="E80" s="3"/>
-      <c r="M80" s="3"/>
+    <row r="71" customHeight="1" spans="8:8">
+      <c r="H71" s="1"/>
     </row>
     <row r="81" customHeight="1" spans="4:13">
       <c r="D81" s="3"/>
@@ -2269,6 +2270,11 @@
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="M85" s="3"/>
+    </row>
+    <row r="86" customHeight="1" spans="4:13">
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="M86" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -2410,7 +2416,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E6" s="1">
         <v>7</v>
@@ -2425,16 +2431,16 @@
         <v>2</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="3:12">
